--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,3183 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120088867</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>777364</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7298811</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120088857</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>777367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7298814</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120088850</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>777502</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7298806</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120088834</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>777529</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7299081</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120088865</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>777415</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7298849</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120088842</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>777507</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7299126</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120088864</v>
+      </c>
+      <c r="B9" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>777355</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7298843</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120088868</v>
+      </c>
+      <c r="B10" t="n">
+        <v>95202</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>777492</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7299157</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120088855</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>777392</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7298835</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120088845</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>777508</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7298912</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120088863</v>
+      </c>
+      <c r="B13" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>777515</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7299124</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120088827</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87406</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>777473</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7298817</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120088851</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>777457</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7298804</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120088854</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>777398</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7298832</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120088858</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>777356</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7298837</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120088853</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>777429</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7298824</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120088846</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>777509</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7298862</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120088840</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>777485</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7299147</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120088870</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95202</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>777507</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7299148</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120088869</v>
+      </c>
+      <c r="B22" t="n">
+        <v>95202</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>777505</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7299155</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120088866</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>777389</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7298847</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120088856</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>777378</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7298811</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120088849</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>777511</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7298804</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120088847</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>777517</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7298828</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120088828</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79144</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>777455</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7298795</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120088829</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>777417</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7298838</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120088862</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>777412</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7298815</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120088831</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79636</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>777532</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7299086</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120088852</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>777427</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7298810</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120088841</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>777505</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7299152</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120088843</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>777504</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7298945</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3962,6 +3962,1638 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120109459</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>777599</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7299147</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120109454</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>777458</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7298865</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120109444</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>777573</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7299187</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120109452</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>777449</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7298879</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120109457</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>777600</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7299114</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120109453</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>777456</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7298884</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120109455</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>777511</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7298851</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120109449</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>777456</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7298953</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120109451</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>777444</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7298882</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120109446</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>777434</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7298954</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120109450</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>777403</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7298895</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120109445</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>777555</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7299109</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120109443</v>
+      </c>
+      <c r="B46" t="n">
+        <v>96868</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>777444</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7298925</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120109447</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>777398</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7298959</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120109465</v>
+      </c>
+      <c r="B48" t="n">
+        <v>82305</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>777595</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7299138</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120109448</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>777417</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7298952</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088867</v>
+        <v>120088858</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -821,20 +821,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777364</v>
+        <v>777356</v>
       </c>
       <c r="R3" t="n">
-        <v>7298811</v>
+        <v>7298837</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088857</v>
+        <v>120088831</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777367</v>
+        <v>777532</v>
       </c>
       <c r="R4" t="n">
-        <v>7298814</v>
+        <v>7299086</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088850</v>
+        <v>120088841</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777502</v>
+        <v>777505</v>
       </c>
       <c r="R5" t="n">
-        <v>7298806</v>
+        <v>7299152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088834</v>
+        <v>120088857</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777529</v>
+        <v>777367</v>
       </c>
       <c r="R6" t="n">
-        <v>7299081</v>
+        <v>7298814</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088865</v>
+        <v>120088855</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1234,20 +1229,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777415</v>
+        <v>777392</v>
       </c>
       <c r="R7" t="n">
-        <v>7298849</v>
+        <v>7298835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1279,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1300,7 +1290,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088864</v>
+        <v>120088852</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777355</v>
+        <v>777427</v>
       </c>
       <c r="R9" t="n">
-        <v>7298843</v>
+        <v>7298810</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,37 +1501,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088868</v>
+        <v>120088847</v>
       </c>
       <c r="B10" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777492</v>
+        <v>777517</v>
       </c>
       <c r="R10" t="n">
-        <v>7299157</v>
+        <v>7298828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088855</v>
+        <v>120088867</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1647,16 +1637,20 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777392</v>
+        <v>777364</v>
       </c>
       <c r="R11" t="n">
-        <v>7298835</v>
+        <v>7298811</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,6 +1691,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1708,14 +1703,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088845</v>
+        <v>120088853</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777508</v>
+        <v>777429</v>
       </c>
       <c r="R12" t="n">
-        <v>7298912</v>
+        <v>7298824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088863</v>
+        <v>120088828</v>
       </c>
       <c r="B13" t="n">
-        <v>82305</v>
+        <v>79144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777515</v>
+        <v>777455</v>
       </c>
       <c r="R13" t="n">
-        <v>7299124</v>
+        <v>7298795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088827</v>
+        <v>120088834</v>
       </c>
       <c r="B14" t="n">
-        <v>87406</v>
+        <v>79607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4412</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777473</v>
+        <v>777529</v>
       </c>
       <c r="R14" t="n">
-        <v>7298817</v>
+        <v>7299081</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088851</v>
+        <v>120088840</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777457</v>
+        <v>777485</v>
       </c>
       <c r="R15" t="n">
-        <v>7298804</v>
+        <v>7299147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088854</v>
+        <v>120088863</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777398</v>
+        <v>777515</v>
       </c>
       <c r="R16" t="n">
-        <v>7298832</v>
+        <v>7299124</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088858</v>
+        <v>120088870</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777356</v>
+        <v>777507</v>
       </c>
       <c r="R17" t="n">
-        <v>7298837</v>
+        <v>7299148</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088853</v>
+        <v>120088865</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2361,16 +2356,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777429</v>
+        <v>777415</v>
       </c>
       <c r="R18" t="n">
-        <v>7298824</v>
+        <v>7298849</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,6 +2410,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2531,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088840</v>
+        <v>120088827</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2543,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777485</v>
+        <v>777473</v>
       </c>
       <c r="R20" t="n">
-        <v>7299147</v>
+        <v>7298817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088870</v>
+        <v>120088845</v>
       </c>
       <c r="B21" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777507</v>
+        <v>777508</v>
       </c>
       <c r="R21" t="n">
-        <v>7299148</v>
+        <v>7298912</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088869</v>
+        <v>120088843</v>
       </c>
       <c r="B22" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2747,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777505</v>
+        <v>777504</v>
       </c>
       <c r="R22" t="n">
-        <v>7299155</v>
+        <v>7298945</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088866</v>
+        <v>120088849</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -2871,20 +2871,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777389</v>
+        <v>777511</v>
       </c>
       <c r="R23" t="n">
-        <v>7298847</v>
+        <v>7298804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2921,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2937,14 +2932,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088856</v>
+        <v>120088851</v>
       </c>
       <c r="B24" t="n">
         <v>97907</v>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777378</v>
+        <v>777457</v>
       </c>
       <c r="R24" t="n">
-        <v>7298811</v>
+        <v>7298804</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,37 +3041,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088849</v>
+        <v>120088868</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777511</v>
+        <v>777492</v>
       </c>
       <c r="R25" t="n">
-        <v>7298804</v>
+        <v>7299157</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088847</v>
+        <v>120088864</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777517</v>
+        <v>777355</v>
       </c>
       <c r="R26" t="n">
-        <v>7298828</v>
+        <v>7298843</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088828</v>
+        <v>120088829</v>
       </c>
       <c r="B27" t="n">
-        <v>79144</v>
+        <v>90527</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3257,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777455</v>
+        <v>777417</v>
       </c>
       <c r="R27" t="n">
-        <v>7298795</v>
+        <v>7298838</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088829</v>
+        <v>120088866</v>
       </c>
       <c r="B28" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,38 +3359,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777417</v>
+        <v>777389</v>
       </c>
       <c r="R28" t="n">
-        <v>7298838</v>
+        <v>7298847</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3436,6 +3435,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088831</v>
+        <v>120088856</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3568,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777532</v>
+        <v>777378</v>
       </c>
       <c r="R30" t="n">
-        <v>7299086</v>
+        <v>7298811</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088852</v>
+        <v>120088850</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777427</v>
+        <v>777502</v>
       </c>
       <c r="R31" t="n">
-        <v>7298810</v>
+        <v>7298806</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088841</v>
+        <v>120088854</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777505</v>
+        <v>777398</v>
       </c>
       <c r="R32" t="n">
-        <v>7299152</v>
+        <v>7298832</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088843</v>
+        <v>120088869</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777504</v>
+        <v>777505</v>
       </c>
       <c r="R33" t="n">
-        <v>7298945</v>
+        <v>7299155</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109459</v>
+        <v>120109451</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777599</v>
+        <v>777444</v>
       </c>
       <c r="R34" t="n">
-        <v>7299147</v>
+        <v>7298882</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109454</v>
+        <v>120109450</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777458</v>
+        <v>777403</v>
       </c>
       <c r="R35" t="n">
-        <v>7298865</v>
+        <v>7298895</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109452</v>
+        <v>120109457</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777449</v>
+        <v>777600</v>
       </c>
       <c r="R37" t="n">
-        <v>7298879</v>
+        <v>7299114</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109457</v>
+        <v>120109465</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777600</v>
+        <v>777595</v>
       </c>
       <c r="R38" t="n">
-        <v>7299114</v>
+        <v>7299138</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109453</v>
+        <v>120109447</v>
       </c>
       <c r="B39" t="n">
         <v>97907</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777456</v>
+        <v>777398</v>
       </c>
       <c r="R39" t="n">
-        <v>7298884</v>
+        <v>7298959</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109455</v>
+        <v>120109448</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777511</v>
+        <v>777417</v>
       </c>
       <c r="R40" t="n">
-        <v>7298851</v>
+        <v>7298952</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109449</v>
+        <v>120109453</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -4721,7 +4721,7 @@
         <v>777456</v>
       </c>
       <c r="R41" t="n">
-        <v>7298953</v>
+        <v>7298884</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109451</v>
+        <v>120109455</v>
       </c>
       <c r="B42" t="n">
         <v>97907</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777444</v>
+        <v>777511</v>
       </c>
       <c r="R42" t="n">
-        <v>7298882</v>
+        <v>7298851</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109446</v>
+        <v>120109449</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777434</v>
+        <v>777456</v>
       </c>
       <c r="R43" t="n">
-        <v>7298954</v>
+        <v>7298953</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109450</v>
+        <v>120109454</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777403</v>
+        <v>777458</v>
       </c>
       <c r="R44" t="n">
-        <v>7298895</v>
+        <v>7298865</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109445</v>
+        <v>120109446</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777555</v>
+        <v>777434</v>
       </c>
       <c r="R45" t="n">
-        <v>7299109</v>
+        <v>7298954</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109443</v>
+        <v>120109459</v>
       </c>
       <c r="B46" t="n">
-        <v>96868</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5200,25 +5200,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777444</v>
+        <v>777599</v>
       </c>
       <c r="R46" t="n">
-        <v>7298925</v>
+        <v>7299147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109447</v>
+        <v>120109452</v>
       </c>
       <c r="B47" t="n">
         <v>97907</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777398</v>
+        <v>777449</v>
       </c>
       <c r="R47" t="n">
-        <v>7298959</v>
+        <v>7298879</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109465</v>
+        <v>120109445</v>
       </c>
       <c r="B48" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5404,25 +5404,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777595</v>
+        <v>777555</v>
       </c>
       <c r="R48" t="n">
-        <v>7299138</v>
+        <v>7299109</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109448</v>
+        <v>120109443</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>96868</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5506,25 +5506,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777417</v>
+        <v>777444</v>
       </c>
       <c r="R49" t="n">
-        <v>7298952</v>
+        <v>7298925</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088858</v>
+        <v>120088831</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777356</v>
+        <v>777532</v>
       </c>
       <c r="R3" t="n">
-        <v>7298837</v>
+        <v>7299086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088831</v>
+        <v>120088858</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777532</v>
+        <v>777356</v>
       </c>
       <c r="R4" t="n">
-        <v>7299086</v>
+        <v>7298837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088840</v>
+        <v>120088863</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777485</v>
+        <v>777515</v>
       </c>
       <c r="R15" t="n">
-        <v>7299147</v>
+        <v>7299124</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088863</v>
+        <v>120088840</v>
       </c>
       <c r="B16" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777515</v>
+        <v>777485</v>
       </c>
       <c r="R16" t="n">
-        <v>7299124</v>
+        <v>7299147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109455</v>
+        <v>120109449</v>
       </c>
       <c r="B42" t="n">
         <v>97907</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777511</v>
+        <v>777456</v>
       </c>
       <c r="R42" t="n">
-        <v>7298851</v>
+        <v>7298953</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109449</v>
+        <v>120109455</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777456</v>
+        <v>777511</v>
       </c>
       <c r="R43" t="n">
-        <v>7298953</v>
+        <v>7298851</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088831</v>
+        <v>120088870</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>95202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777532</v>
+        <v>777507</v>
       </c>
       <c r="R3" t="n">
-        <v>7299086</v>
+        <v>7299148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088858</v>
+        <v>120088827</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777356</v>
+        <v>777473</v>
       </c>
       <c r="R4" t="n">
-        <v>7298837</v>
+        <v>7298817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088841</v>
+        <v>120088858</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777505</v>
+        <v>777356</v>
       </c>
       <c r="R5" t="n">
-        <v>7299152</v>
+        <v>7298837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088857</v>
+        <v>120088828</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>79144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777367</v>
+        <v>777455</v>
       </c>
       <c r="R6" t="n">
-        <v>7298814</v>
+        <v>7298795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088855</v>
+        <v>120088865</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1229,16 +1229,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777392</v>
+        <v>777415</v>
       </c>
       <c r="R7" t="n">
-        <v>7298835</v>
+        <v>7298849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,6 +1283,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,14 +1295,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088842</v>
+        <v>120088843</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777507</v>
+        <v>777504</v>
       </c>
       <c r="R8" t="n">
-        <v>7299126</v>
+        <v>7298945</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088852</v>
+        <v>120088847</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777427</v>
+        <v>777517</v>
       </c>
       <c r="R9" t="n">
-        <v>7298810</v>
+        <v>7298828</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088847</v>
+        <v>120088864</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777517</v>
+        <v>777355</v>
       </c>
       <c r="R10" t="n">
-        <v>7298828</v>
+        <v>7298843</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088867</v>
+        <v>120088862</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,42 +1620,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777364</v>
+        <v>777412</v>
       </c>
       <c r="R11" t="n">
-        <v>7298811</v>
+        <v>7298815</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,7 +1692,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1703,17 +1703,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088853</v>
+        <v>120088834</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777429</v>
+        <v>777529</v>
       </c>
       <c r="R12" t="n">
-        <v>7298824</v>
+        <v>7299081</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088828</v>
+        <v>120088854</v>
       </c>
       <c r="B13" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777455</v>
+        <v>777398</v>
       </c>
       <c r="R13" t="n">
-        <v>7298795</v>
+        <v>7298832</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088834</v>
+        <v>120088846</v>
       </c>
       <c r="B14" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777529</v>
+        <v>777509</v>
       </c>
       <c r="R14" t="n">
-        <v>7299081</v>
+        <v>7298862</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088863</v>
+        <v>120088831</v>
       </c>
       <c r="B15" t="n">
-        <v>82305</v>
+        <v>79636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777515</v>
+        <v>777532</v>
       </c>
       <c r="R15" t="n">
-        <v>7299124</v>
+        <v>7299086</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088840</v>
+        <v>120088845</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777485</v>
+        <v>777508</v>
       </c>
       <c r="R16" t="n">
-        <v>7299147</v>
+        <v>7298912</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088870</v>
+        <v>120088850</v>
       </c>
       <c r="B17" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777507</v>
+        <v>777502</v>
       </c>
       <c r="R17" t="n">
-        <v>7299148</v>
+        <v>7298806</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088865</v>
+        <v>120088856</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2356,20 +2356,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777415</v>
+        <v>777378</v>
       </c>
       <c r="R18" t="n">
-        <v>7298849</v>
+        <v>7298811</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2406,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2422,17 +2417,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088846</v>
+        <v>120088869</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2436,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777509</v>
+        <v>777505</v>
       </c>
       <c r="R19" t="n">
-        <v>7298862</v>
+        <v>7299155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,37 +2526,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088827</v>
+        <v>120088868</v>
       </c>
       <c r="B20" t="n">
-        <v>87406</v>
+        <v>95202</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4412</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777473</v>
+        <v>777492</v>
       </c>
       <c r="R20" t="n">
-        <v>7298817</v>
+        <v>7299157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088845</v>
+        <v>120088841</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2673,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777508</v>
+        <v>777505</v>
       </c>
       <c r="R21" t="n">
-        <v>7298912</v>
+        <v>7299152</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088843</v>
+        <v>120088840</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2775,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777504</v>
+        <v>777485</v>
       </c>
       <c r="R22" t="n">
-        <v>7298945</v>
+        <v>7299147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088849</v>
+        <v>120088842</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -2877,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777511</v>
+        <v>777507</v>
       </c>
       <c r="R23" t="n">
-        <v>7298804</v>
+        <v>7299126</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088851</v>
+        <v>120088829</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2946,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777457</v>
+        <v>777417</v>
       </c>
       <c r="R24" t="n">
-        <v>7298804</v>
+        <v>7298838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,50 +3036,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088868</v>
+        <v>120088866</v>
       </c>
       <c r="B25" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777492</v>
+        <v>777389</v>
       </c>
       <c r="R25" t="n">
-        <v>7299157</v>
+        <v>7298847</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,6 +3124,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,17 +3136,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088864</v>
+        <v>120088857</v>
       </c>
       <c r="B26" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777355</v>
+        <v>777367</v>
       </c>
       <c r="R26" t="n">
-        <v>7298843</v>
+        <v>7298814</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088829</v>
+        <v>120088849</v>
       </c>
       <c r="B27" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,25 +3257,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777417</v>
+        <v>777511</v>
       </c>
       <c r="R27" t="n">
-        <v>7298838</v>
+        <v>7298804</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088866</v>
+        <v>120088852</v>
       </c>
       <c r="B28" t="n">
         <v>97907</v>
@@ -3381,20 +3381,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777389</v>
+        <v>777427</v>
       </c>
       <c r="R28" t="n">
-        <v>7298847</v>
+        <v>7298810</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,7 +3431,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3447,17 +3442,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088862</v>
+        <v>120088863</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,21 +3465,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777412</v>
+        <v>777515</v>
       </c>
       <c r="R29" t="n">
-        <v>7298815</v>
+        <v>7299124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3551,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088856</v>
+        <v>120088853</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3596,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777378</v>
+        <v>777429</v>
       </c>
       <c r="R30" t="n">
-        <v>7298811</v>
+        <v>7298824</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088850</v>
+        <v>120088867</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -3692,16 +3687,20 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777502</v>
+        <v>777364</v>
       </c>
       <c r="R31" t="n">
-        <v>7298806</v>
+        <v>7298811</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,6 +3741,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088854</v>
+        <v>120088855</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777398</v>
+        <v>777392</v>
       </c>
       <c r="R32" t="n">
-        <v>7298832</v>
+        <v>7298835</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088869</v>
+        <v>120088851</v>
       </c>
       <c r="B33" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777505</v>
+        <v>777457</v>
       </c>
       <c r="R33" t="n">
-        <v>7299155</v>
+        <v>7298804</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109451</v>
+        <v>120109457</v>
       </c>
       <c r="B34" t="n">
         <v>97907</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777444</v>
+        <v>777600</v>
       </c>
       <c r="R34" t="n">
-        <v>7298882</v>
+        <v>7299114</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109450</v>
+        <v>120109453</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777403</v>
+        <v>777456</v>
       </c>
       <c r="R35" t="n">
-        <v>7298895</v>
+        <v>7298884</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109444</v>
+        <v>120109448</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777573</v>
+        <v>777417</v>
       </c>
       <c r="R36" t="n">
-        <v>7299187</v>
+        <v>7298952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109457</v>
+        <v>120109444</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777600</v>
+        <v>777573</v>
       </c>
       <c r="R37" t="n">
-        <v>7299114</v>
+        <v>7299187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109465</v>
+        <v>120109449</v>
       </c>
       <c r="B38" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777595</v>
+        <v>777456</v>
       </c>
       <c r="R38" t="n">
-        <v>7299138</v>
+        <v>7298953</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109447</v>
+        <v>120109445</v>
       </c>
       <c r="B39" t="n">
         <v>97907</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777398</v>
+        <v>777555</v>
       </c>
       <c r="R39" t="n">
-        <v>7298959</v>
+        <v>7299109</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109448</v>
+        <v>120109451</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777417</v>
+        <v>777444</v>
       </c>
       <c r="R40" t="n">
-        <v>7298952</v>
+        <v>7298882</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109453</v>
+        <v>120109447</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777456</v>
+        <v>777398</v>
       </c>
       <c r="R41" t="n">
-        <v>7298884</v>
+        <v>7298959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109449</v>
+        <v>120109455</v>
       </c>
       <c r="B42" t="n">
         <v>97907</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777456</v>
+        <v>777511</v>
       </c>
       <c r="R42" t="n">
-        <v>7298953</v>
+        <v>7298851</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109455</v>
+        <v>120109452</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777511</v>
+        <v>777449</v>
       </c>
       <c r="R43" t="n">
-        <v>7298851</v>
+        <v>7298879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109454</v>
+        <v>120109446</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777458</v>
+        <v>777434</v>
       </c>
       <c r="R44" t="n">
-        <v>7298865</v>
+        <v>7298954</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109446</v>
+        <v>120109459</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777434</v>
+        <v>777599</v>
       </c>
       <c r="R45" t="n">
-        <v>7298954</v>
+        <v>7299147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109459</v>
+        <v>120109454</v>
       </c>
       <c r="B46" t="n">
         <v>97907</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777599</v>
+        <v>777458</v>
       </c>
       <c r="R46" t="n">
-        <v>7299147</v>
+        <v>7298865</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109452</v>
+        <v>120109443</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>96868</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5302,25 +5302,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777449</v>
+        <v>777444</v>
       </c>
       <c r="R47" t="n">
-        <v>7298879</v>
+        <v>7298925</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109445</v>
+        <v>120109465</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5404,25 +5404,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777555</v>
+        <v>777595</v>
       </c>
       <c r="R48" t="n">
-        <v>7299109</v>
+        <v>7299138</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109443</v>
+        <v>120109450</v>
       </c>
       <c r="B49" t="n">
-        <v>96868</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5506,25 +5506,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777444</v>
+        <v>777403</v>
       </c>
       <c r="R49" t="n">
-        <v>7298925</v>
+        <v>7298895</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088827</v>
+        <v>120088828</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777473</v>
+        <v>777455</v>
       </c>
       <c r="R4" t="n">
-        <v>7298817</v>
+        <v>7298795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088858</v>
+        <v>120088827</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777356</v>
+        <v>777473</v>
       </c>
       <c r="R5" t="n">
-        <v>7298837</v>
+        <v>7298817</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088828</v>
+        <v>120088858</v>
       </c>
       <c r="B6" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777455</v>
+        <v>777356</v>
       </c>
       <c r="R6" t="n">
-        <v>7298795</v>
+        <v>7298837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088831</v>
+        <v>120088845</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777532</v>
+        <v>777508</v>
       </c>
       <c r="R15" t="n">
-        <v>7299086</v>
+        <v>7298912</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088845</v>
+        <v>120088850</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777508</v>
+        <v>777502</v>
       </c>
       <c r="R16" t="n">
-        <v>7298912</v>
+        <v>7298806</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088850</v>
+        <v>120088831</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777502</v>
+        <v>777532</v>
       </c>
       <c r="R17" t="n">
-        <v>7298806</v>
+        <v>7299086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088870</v>
+        <v>120088866</v>
       </c>
       <c r="B3" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777507</v>
+        <v>777389</v>
       </c>
       <c r="R3" t="n">
-        <v>7299148</v>
+        <v>7298847</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,17 +887,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088828</v>
+        <v>120088858</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777455</v>
+        <v>777356</v>
       </c>
       <c r="R4" t="n">
-        <v>7298795</v>
+        <v>7298837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088827</v>
+        <v>120088831</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
+        <v>79636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4412</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777473</v>
+        <v>777532</v>
       </c>
       <c r="R5" t="n">
-        <v>7298817</v>
+        <v>7299086</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088858</v>
+        <v>120088853</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777356</v>
+        <v>777429</v>
       </c>
       <c r="R6" t="n">
-        <v>7298837</v>
+        <v>7298824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088865</v>
+        <v>120088843</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1229,20 +1234,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777415</v>
+        <v>777504</v>
       </c>
       <c r="R7" t="n">
-        <v>7298849</v>
+        <v>7298945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1284,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,14 +1295,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088843</v>
+        <v>120088847</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777504</v>
+        <v>777517</v>
       </c>
       <c r="R8" t="n">
-        <v>7298945</v>
+        <v>7298828</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088847</v>
+        <v>120088840</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777517</v>
+        <v>777485</v>
       </c>
       <c r="R9" t="n">
-        <v>7298828</v>
+        <v>7299147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088864</v>
+        <v>120088854</v>
       </c>
       <c r="B10" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777355</v>
+        <v>777398</v>
       </c>
       <c r="R10" t="n">
-        <v>7298843</v>
+        <v>7298832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088862</v>
+        <v>120088828</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777412</v>
+        <v>777455</v>
       </c>
       <c r="R11" t="n">
-        <v>7298815</v>
+        <v>7298795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088834</v>
+        <v>120088829</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777529</v>
+        <v>777417</v>
       </c>
       <c r="R12" t="n">
-        <v>7299081</v>
+        <v>7298838</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088854</v>
+        <v>120088842</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777398</v>
+        <v>777507</v>
       </c>
       <c r="R13" t="n">
-        <v>7298832</v>
+        <v>7299126</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088846</v>
+        <v>120088856</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777509</v>
+        <v>777378</v>
       </c>
       <c r="R14" t="n">
-        <v>7298862</v>
+        <v>7298811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088850</v>
+        <v>120088864</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777502</v>
+        <v>777355</v>
       </c>
       <c r="R16" t="n">
-        <v>7298806</v>
+        <v>7298843</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088831</v>
+        <v>120088863</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>82305</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777532</v>
+        <v>777515</v>
       </c>
       <c r="R17" t="n">
-        <v>7299086</v>
+        <v>7299124</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088856</v>
+        <v>120088869</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777378</v>
+        <v>777505</v>
       </c>
       <c r="R18" t="n">
-        <v>7298811</v>
+        <v>7299155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088869</v>
+        <v>120088857</v>
       </c>
       <c r="B19" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2436,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777505</v>
+        <v>777367</v>
       </c>
       <c r="R19" t="n">
-        <v>7299155</v>
+        <v>7298814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,50 +2526,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088868</v>
+        <v>120088867</v>
       </c>
       <c r="B20" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777492</v>
+        <v>777364</v>
       </c>
       <c r="R20" t="n">
-        <v>7299157</v>
+        <v>7298811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,6 +2614,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2621,7 +2626,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2730,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088840</v>
+        <v>120088851</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2770,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777485</v>
+        <v>777457</v>
       </c>
       <c r="R22" t="n">
-        <v>7299147</v>
+        <v>7298804</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088842</v>
+        <v>120088855</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -2872,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777507</v>
+        <v>777392</v>
       </c>
       <c r="R23" t="n">
-        <v>7299126</v>
+        <v>7298835</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088829</v>
+        <v>120088862</v>
       </c>
       <c r="B24" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2974,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777417</v>
+        <v>777412</v>
       </c>
       <c r="R24" t="n">
-        <v>7298838</v>
+        <v>7298815</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088866</v>
+        <v>120088850</v>
       </c>
       <c r="B25" t="n">
         <v>97907</v>
@@ -3070,20 +3075,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777389</v>
+        <v>777502</v>
       </c>
       <c r="R25" t="n">
-        <v>7298847</v>
+        <v>7298806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,7 +3125,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,17 +3136,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088857</v>
+        <v>120088827</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>87406</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777367</v>
+        <v>777473</v>
       </c>
       <c r="R26" t="n">
-        <v>7298814</v>
+        <v>7298817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088849</v>
+        <v>120088870</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,25 +3257,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777511</v>
+        <v>777507</v>
       </c>
       <c r="R27" t="n">
-        <v>7298804</v>
+        <v>7299148</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,37 +3347,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088852</v>
+        <v>120088868</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777427</v>
+        <v>777492</v>
       </c>
       <c r="R28" t="n">
-        <v>7298810</v>
+        <v>7299157</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088863</v>
+        <v>120088849</v>
       </c>
       <c r="B29" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777515</v>
+        <v>777511</v>
       </c>
       <c r="R29" t="n">
-        <v>7299124</v>
+        <v>7298804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088853</v>
+        <v>120088865</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -3585,16 +3585,20 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777429</v>
+        <v>777415</v>
       </c>
       <c r="R30" t="n">
-        <v>7298824</v>
+        <v>7298849</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,6 +3639,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3646,17 +3651,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088867</v>
+        <v>120088834</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,42 +3670,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777364</v>
+        <v>777529</v>
       </c>
       <c r="R31" t="n">
-        <v>7298811</v>
+        <v>7299081</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3741,7 +3742,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3753,14 +3753,14 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088855</v>
+        <v>120088846</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777392</v>
+        <v>777509</v>
       </c>
       <c r="R32" t="n">
-        <v>7298835</v>
+        <v>7298862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088851</v>
+        <v>120088852</v>
       </c>
       <c r="B33" t="n">
         <v>97907</v>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777457</v>
+        <v>777427</v>
       </c>
       <c r="R33" t="n">
-        <v>7298804</v>
+        <v>7298810</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109457</v>
+        <v>120109465</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>82305</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777600</v>
+        <v>777595</v>
       </c>
       <c r="R34" t="n">
-        <v>7299114</v>
+        <v>7299138</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109453</v>
+        <v>120109452</v>
       </c>
       <c r="B35" t="n">
         <v>97907</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777456</v>
+        <v>777449</v>
       </c>
       <c r="R35" t="n">
-        <v>7298884</v>
+        <v>7298879</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109448</v>
+        <v>120109459</v>
       </c>
       <c r="B36" t="n">
         <v>97907</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777417</v>
+        <v>777599</v>
       </c>
       <c r="R36" t="n">
-        <v>7298952</v>
+        <v>7299147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109444</v>
+        <v>120109448</v>
       </c>
       <c r="B37" t="n">
         <v>97907</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777573</v>
+        <v>777417</v>
       </c>
       <c r="R37" t="n">
-        <v>7299187</v>
+        <v>7298952</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109445</v>
+        <v>120109451</v>
       </c>
       <c r="B39" t="n">
         <v>97907</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777555</v>
+        <v>777444</v>
       </c>
       <c r="R39" t="n">
-        <v>7299109</v>
+        <v>7298882</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109451</v>
+        <v>120109446</v>
       </c>
       <c r="B40" t="n">
         <v>97907</v>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777444</v>
+        <v>777434</v>
       </c>
       <c r="R40" t="n">
-        <v>7298882</v>
+        <v>7298954</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109447</v>
+        <v>120109450</v>
       </c>
       <c r="B41" t="n">
         <v>97907</v>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777398</v>
+        <v>777403</v>
       </c>
       <c r="R41" t="n">
-        <v>7298959</v>
+        <v>7298895</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109455</v>
+        <v>120109447</v>
       </c>
       <c r="B42" t="n">
         <v>97907</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777511</v>
+        <v>777398</v>
       </c>
       <c r="R42" t="n">
-        <v>7298851</v>
+        <v>7298959</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109452</v>
+        <v>120109444</v>
       </c>
       <c r="B43" t="n">
         <v>97907</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777449</v>
+        <v>777573</v>
       </c>
       <c r="R43" t="n">
-        <v>7298879</v>
+        <v>7299187</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109446</v>
+        <v>120109443</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>96868</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4996,25 +4996,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777434</v>
+        <v>777444</v>
       </c>
       <c r="R44" t="n">
-        <v>7298954</v>
+        <v>7298925</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109459</v>
+        <v>120109454</v>
       </c>
       <c r="B45" t="n">
         <v>97907</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777599</v>
+        <v>777458</v>
       </c>
       <c r="R45" t="n">
-        <v>7299147</v>
+        <v>7298865</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109454</v>
+        <v>120109455</v>
       </c>
       <c r="B46" t="n">
         <v>97907</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777458</v>
+        <v>777511</v>
       </c>
       <c r="R46" t="n">
-        <v>7298865</v>
+        <v>7298851</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109443</v>
+        <v>120109445</v>
       </c>
       <c r="B47" t="n">
-        <v>96868</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5302,25 +5302,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777444</v>
+        <v>777555</v>
       </c>
       <c r="R47" t="n">
-        <v>7298925</v>
+        <v>7299109</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109465</v>
+        <v>120109457</v>
       </c>
       <c r="B48" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5404,25 +5404,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777595</v>
+        <v>777600</v>
       </c>
       <c r="R48" t="n">
-        <v>7299138</v>
+        <v>7299114</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109450</v>
+        <v>120109453</v>
       </c>
       <c r="B49" t="n">
         <v>97907</v>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777403</v>
+        <v>777456</v>
       </c>
       <c r="R49" t="n">
-        <v>7298895</v>
+        <v>7298884</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088840</v>
+        <v>120088829</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777485</v>
+        <v>777417</v>
       </c>
       <c r="R9" t="n">
-        <v>7299147</v>
+        <v>7298838</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088854</v>
+        <v>120088840</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777398</v>
+        <v>777485</v>
       </c>
       <c r="R10" t="n">
-        <v>7298832</v>
+        <v>7299147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088828</v>
+        <v>120088854</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777455</v>
+        <v>777398</v>
       </c>
       <c r="R11" t="n">
-        <v>7298795</v>
+        <v>7298832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088829</v>
+        <v>120088828</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>79144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777417</v>
+        <v>777455</v>
       </c>
       <c r="R12" t="n">
-        <v>7298838</v>
+        <v>7298795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088849</v>
+        <v>120088834</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777511</v>
+        <v>777529</v>
       </c>
       <c r="R29" t="n">
-        <v>7298804</v>
+        <v>7299081</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088834</v>
+        <v>120088849</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777529</v>
+        <v>777511</v>
       </c>
       <c r="R31" t="n">
-        <v>7299081</v>
+        <v>7298804</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088829</v>
+        <v>120088840</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777417</v>
+        <v>777485</v>
       </c>
       <c r="R9" t="n">
-        <v>7298838</v>
+        <v>7299147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088840</v>
+        <v>120088854</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777485</v>
+        <v>777398</v>
       </c>
       <c r="R10" t="n">
-        <v>7299147</v>
+        <v>7298832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088854</v>
+        <v>120088828</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777398</v>
+        <v>777455</v>
       </c>
       <c r="R11" t="n">
-        <v>7298832</v>
+        <v>7298795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088828</v>
+        <v>120088829</v>
       </c>
       <c r="B12" t="n">
-        <v>79144</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777455</v>
+        <v>777417</v>
       </c>
       <c r="R12" t="n">
-        <v>7298795</v>
+        <v>7298838</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088834</v>
+        <v>120088849</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777529</v>
+        <v>777511</v>
       </c>
       <c r="R29" t="n">
-        <v>7299081</v>
+        <v>7298804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088849</v>
+        <v>120088834</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777511</v>
+        <v>777529</v>
       </c>
       <c r="R31" t="n">
-        <v>7298804</v>
+        <v>7299081</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -3449,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088849</v>
+        <v>120088834</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777511</v>
+        <v>777529</v>
       </c>
       <c r="R29" t="n">
-        <v>7298804</v>
+        <v>7299081</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088834</v>
+        <v>120088849</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777529</v>
+        <v>777511</v>
       </c>
       <c r="R31" t="n">
-        <v>7299081</v>
+        <v>7298804</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088841</v>
+        <v>120088862</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777505</v>
+        <v>777412</v>
       </c>
       <c r="R21" t="n">
-        <v>7299152</v>
+        <v>7298815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088851</v>
+        <v>120088841</v>
       </c>
       <c r="B22" t="n">
         <v>97907</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777457</v>
+        <v>777505</v>
       </c>
       <c r="R22" t="n">
-        <v>7298804</v>
+        <v>7299152</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088855</v>
+        <v>120088851</v>
       </c>
       <c r="B23" t="n">
         <v>97907</v>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777392</v>
+        <v>777457</v>
       </c>
       <c r="R23" t="n">
-        <v>7298835</v>
+        <v>7298804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088862</v>
+        <v>120088855</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777412</v>
+        <v>777392</v>
       </c>
       <c r="R24" t="n">
-        <v>7298815</v>
+        <v>7298835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088834</v>
+        <v>120088849</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777529</v>
+        <v>777511</v>
       </c>
       <c r="R29" t="n">
-        <v>7299081</v>
+        <v>7298804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088849</v>
+        <v>120088834</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777511</v>
+        <v>777529</v>
       </c>
       <c r="R31" t="n">
-        <v>7298804</v>
+        <v>7299081</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088840</v>
+        <v>120088829</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777485</v>
+        <v>777417</v>
       </c>
       <c r="R9" t="n">
-        <v>7299147</v>
+        <v>7298838</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088854</v>
+        <v>120088840</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777398</v>
+        <v>777485</v>
       </c>
       <c r="R10" t="n">
-        <v>7298832</v>
+        <v>7299147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088828</v>
+        <v>120088854</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777455</v>
+        <v>777398</v>
       </c>
       <c r="R11" t="n">
-        <v>7298795</v>
+        <v>7298832</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088829</v>
+        <v>120088828</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>79144</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777417</v>
+        <v>777455</v>
       </c>
       <c r="R12" t="n">
-        <v>7298838</v>
+        <v>7298795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088829</v>
+        <v>120088840</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777417</v>
+        <v>777485</v>
       </c>
       <c r="R9" t="n">
-        <v>7298838</v>
+        <v>7299147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088840</v>
+        <v>120088854</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777485</v>
+        <v>777398</v>
       </c>
       <c r="R10" t="n">
-        <v>7299147</v>
+        <v>7298832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088854</v>
+        <v>120088828</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777398</v>
+        <v>777455</v>
       </c>
       <c r="R11" t="n">
-        <v>7298832</v>
+        <v>7298795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088828</v>
+        <v>120088829</v>
       </c>
       <c r="B12" t="n">
-        <v>79144</v>
+        <v>90527</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777455</v>
+        <v>777417</v>
       </c>
       <c r="R12" t="n">
-        <v>7298795</v>
+        <v>7298838</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088866</v>
+        <v>120088850</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,20 +821,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777389</v>
+        <v>777502</v>
       </c>
       <c r="R3" t="n">
-        <v>7298847</v>
+        <v>7298806</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088858</v>
+        <v>120088867</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,16 +923,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777356</v>
+        <v>777364</v>
       </c>
       <c r="R4" t="n">
-        <v>7298837</v>
+        <v>7298811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,17 +989,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088831</v>
+        <v>120088843</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777532</v>
+        <v>777504</v>
       </c>
       <c r="R5" t="n">
-        <v>7299086</v>
+        <v>7298945</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088853</v>
+        <v>120088840</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777429</v>
+        <v>777485</v>
       </c>
       <c r="R6" t="n">
-        <v>7298824</v>
+        <v>7299147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088843</v>
+        <v>120088841</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777504</v>
+        <v>777505</v>
       </c>
       <c r="R7" t="n">
-        <v>7298945</v>
+        <v>7299152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088847</v>
+        <v>120088854</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777517</v>
+        <v>777398</v>
       </c>
       <c r="R8" t="n">
-        <v>7298828</v>
+        <v>7298832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088840</v>
+        <v>120088828</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777485</v>
+        <v>777455</v>
       </c>
       <c r="R9" t="n">
-        <v>7299147</v>
+        <v>7298795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088854</v>
+        <v>120088855</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777398</v>
+        <v>777392</v>
       </c>
       <c r="R10" t="n">
-        <v>7298832</v>
+        <v>7298835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,37 +1608,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088828</v>
+        <v>120088868</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>95225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777455</v>
+        <v>777492</v>
       </c>
       <c r="R11" t="n">
-        <v>7298795</v>
+        <v>7299157</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088829</v>
+        <v>120088870</v>
       </c>
       <c r="B12" t="n">
-        <v>90527</v>
+        <v>95225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777417</v>
+        <v>777507</v>
       </c>
       <c r="R12" t="n">
-        <v>7298838</v>
+        <v>7299148</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088842</v>
+        <v>120088834</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777507</v>
+        <v>777529</v>
       </c>
       <c r="R13" t="n">
-        <v>7299126</v>
+        <v>7299081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088856</v>
+        <v>120088866</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,16 +1948,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777378</v>
+        <v>777389</v>
       </c>
       <c r="R14" t="n">
-        <v>7298811</v>
+        <v>7298847</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +2002,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,17 +2014,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088845</v>
+        <v>120088856</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777508</v>
+        <v>777378</v>
       </c>
       <c r="R15" t="n">
-        <v>7298912</v>
+        <v>7298811</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088864</v>
+        <v>120088851</v>
       </c>
       <c r="B16" t="n">
-        <v>82305</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777355</v>
+        <v>777457</v>
       </c>
       <c r="R16" t="n">
-        <v>7298843</v>
+        <v>7298804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088863</v>
+        <v>120088862</v>
       </c>
       <c r="B17" t="n">
-        <v>82305</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777515</v>
+        <v>777412</v>
       </c>
       <c r="R17" t="n">
-        <v>7299124</v>
+        <v>7298815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088869</v>
+        <v>120088849</v>
       </c>
       <c r="B18" t="n">
-        <v>95202</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777505</v>
+        <v>777511</v>
       </c>
       <c r="R18" t="n">
-        <v>7299155</v>
+        <v>7298804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088857</v>
+        <v>120088869</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>95225</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777367</v>
+        <v>777505</v>
       </c>
       <c r="R19" t="n">
-        <v>7298814</v>
+        <v>7299155</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088867</v>
+        <v>120088845</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2560,20 +2565,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777364</v>
+        <v>777508</v>
       </c>
       <c r="R20" t="n">
-        <v>7298811</v>
+        <v>7298912</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,7 +2615,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,17 +2626,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088862</v>
+        <v>120088846</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777412</v>
+        <v>777509</v>
       </c>
       <c r="R21" t="n">
-        <v>7298815</v>
+        <v>7298862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088841</v>
+        <v>120088847</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777505</v>
+        <v>777517</v>
       </c>
       <c r="R22" t="n">
-        <v>7299152</v>
+        <v>7298828</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088851</v>
+        <v>120088852</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777457</v>
+        <v>777427</v>
       </c>
       <c r="R23" t="n">
-        <v>7298804</v>
+        <v>7298810</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088855</v>
+        <v>120088865</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2973,16 +2973,20 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777392</v>
+        <v>777415</v>
       </c>
       <c r="R24" t="n">
-        <v>7298835</v>
+        <v>7298849</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,6 +3027,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3034,17 +3039,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088850</v>
+        <v>120088857</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3081,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777502</v>
+        <v>777367</v>
       </c>
       <c r="R25" t="n">
-        <v>7298806</v>
+        <v>7298814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088827</v>
+        <v>120088858</v>
       </c>
       <c r="B26" t="n">
-        <v>87406</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3183,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777473</v>
+        <v>777356</v>
       </c>
       <c r="R26" t="n">
-        <v>7298817</v>
+        <v>7298837</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088870</v>
+        <v>120088827</v>
       </c>
       <c r="B27" t="n">
-        <v>95202</v>
+        <v>87423</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2869</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777507</v>
+        <v>777473</v>
       </c>
       <c r="R27" t="n">
-        <v>7299148</v>
+        <v>7298817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,14 +3352,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088868</v>
+        <v>120088831</v>
       </c>
       <c r="B28" t="n">
-        <v>95202</v>
+        <v>79652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3363,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777492</v>
+        <v>777532</v>
       </c>
       <c r="R28" t="n">
-        <v>7299157</v>
+        <v>7299086</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088849</v>
+        <v>120088863</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>82321</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3466,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777511</v>
+        <v>777515</v>
       </c>
       <c r="R29" t="n">
-        <v>7298804</v>
+        <v>7299124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088865</v>
+        <v>120088864</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>82321</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,42 +3568,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777415</v>
+        <v>777355</v>
       </c>
       <c r="R30" t="n">
-        <v>7298849</v>
+        <v>7298843</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,7 +3640,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3651,17 +3651,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088834</v>
+        <v>120088853</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777529</v>
+        <v>777429</v>
       </c>
       <c r="R31" t="n">
-        <v>7299081</v>
+        <v>7298824</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088846</v>
+        <v>120088829</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,25 +3772,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777509</v>
+        <v>777417</v>
       </c>
       <c r="R32" t="n">
-        <v>7298862</v>
+        <v>7298838</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088852</v>
+        <v>120088842</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777427</v>
+        <v>777507</v>
       </c>
       <c r="R33" t="n">
-        <v>7298810</v>
+        <v>7299126</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109465</v>
+        <v>120109450</v>
       </c>
       <c r="B34" t="n">
-        <v>82305</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777595</v>
+        <v>777403</v>
       </c>
       <c r="R34" t="n">
-        <v>7299138</v>
+        <v>7298895</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109452</v>
+        <v>120109445</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777449</v>
+        <v>777555</v>
       </c>
       <c r="R35" t="n">
-        <v>7298879</v>
+        <v>7299109</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109459</v>
+        <v>120109449</v>
       </c>
       <c r="B36" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777599</v>
+        <v>777456</v>
       </c>
       <c r="R36" t="n">
-        <v>7299147</v>
+        <v>7298953</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109448</v>
+        <v>120109452</v>
       </c>
       <c r="B37" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777417</v>
+        <v>777449</v>
       </c>
       <c r="R37" t="n">
-        <v>7298952</v>
+        <v>7298879</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109449</v>
+        <v>120109443</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>96891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777456</v>
+        <v>777444</v>
       </c>
       <c r="R38" t="n">
-        <v>7298953</v>
+        <v>7298925</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109451</v>
+        <v>120109444</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777444</v>
+        <v>777573</v>
       </c>
       <c r="R39" t="n">
-        <v>7298882</v>
+        <v>7299187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109446</v>
+        <v>120109457</v>
       </c>
       <c r="B40" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777434</v>
+        <v>777600</v>
       </c>
       <c r="R40" t="n">
-        <v>7298954</v>
+        <v>7299114</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109450</v>
+        <v>120109459</v>
       </c>
       <c r="B41" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777403</v>
+        <v>777599</v>
       </c>
       <c r="R41" t="n">
-        <v>7298895</v>
+        <v>7299147</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109447</v>
+        <v>120109446</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777398</v>
+        <v>777434</v>
       </c>
       <c r="R42" t="n">
-        <v>7298959</v>
+        <v>7298954</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109444</v>
+        <v>120109447</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777573</v>
+        <v>777398</v>
       </c>
       <c r="R43" t="n">
-        <v>7299187</v>
+        <v>7298959</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109443</v>
+        <v>120109448</v>
       </c>
       <c r="B44" t="n">
-        <v>96868</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4996,25 +4996,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777444</v>
+        <v>777417</v>
       </c>
       <c r="R44" t="n">
-        <v>7298925</v>
+        <v>7298952</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109454</v>
+        <v>120109451</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777458</v>
+        <v>777444</v>
       </c>
       <c r="R45" t="n">
-        <v>7298865</v>
+        <v>7298882</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109455</v>
+        <v>120109465</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>82321</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5200,25 +5200,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777511</v>
+        <v>777595</v>
       </c>
       <c r="R46" t="n">
-        <v>7298851</v>
+        <v>7299138</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,10 +5290,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109445</v>
+        <v>120109455</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777555</v>
+        <v>777511</v>
       </c>
       <c r="R47" t="n">
-        <v>7299109</v>
+        <v>7298851</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109457</v>
+        <v>120109454</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777600</v>
+        <v>777458</v>
       </c>
       <c r="R48" t="n">
-        <v>7299114</v>
+        <v>7298865</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5497,7 +5497,7 @@
         <v>120109453</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088852</v>
+        <v>120088827</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>87423</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777427</v>
+        <v>777473</v>
       </c>
       <c r="R23" t="n">
-        <v>7298810</v>
+        <v>7298817</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088865</v>
+        <v>120088831</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,42 +2951,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777415</v>
+        <v>777532</v>
       </c>
       <c r="R24" t="n">
-        <v>7298849</v>
+        <v>7299086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3027,7 +3023,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3039,14 +3034,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088857</v>
+        <v>120088852</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777367</v>
+        <v>777427</v>
       </c>
       <c r="R25" t="n">
-        <v>7298814</v>
+        <v>7298810</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088858</v>
+        <v>120088865</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3182,16 +3177,20 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777356</v>
+        <v>777415</v>
       </c>
       <c r="R26" t="n">
-        <v>7298837</v>
+        <v>7298849</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3232,6 +3231,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3243,17 +3243,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088827</v>
+        <v>120088857</v>
       </c>
       <c r="B27" t="n">
-        <v>87423</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777473</v>
+        <v>777367</v>
       </c>
       <c r="R27" t="n">
-        <v>7298817</v>
+        <v>7298814</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088831</v>
+        <v>120088858</v>
       </c>
       <c r="B28" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777532</v>
+        <v>777356</v>
       </c>
       <c r="R28" t="n">
-        <v>7299086</v>
+        <v>7298837</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3556,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088864</v>
+        <v>120088853</v>
       </c>
       <c r="B30" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3568,25 +3568,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777355</v>
+        <v>777429</v>
       </c>
       <c r="R30" t="n">
-        <v>7298843</v>
+        <v>7298824</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088853</v>
+        <v>120088864</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777429</v>
+        <v>777355</v>
       </c>
       <c r="R31" t="n">
-        <v>7298824</v>
+        <v>7298843</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109448</v>
+        <v>120109465</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4996,25 +4996,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777417</v>
+        <v>777595</v>
       </c>
       <c r="R44" t="n">
-        <v>7298952</v>
+        <v>7299138</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109451</v>
+        <v>120109448</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777444</v>
+        <v>777417</v>
       </c>
       <c r="R45" t="n">
-        <v>7298882</v>
+        <v>7298952</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5188,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109465</v>
+        <v>120109451</v>
       </c>
       <c r="B46" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5200,25 +5200,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777595</v>
+        <v>777444</v>
       </c>
       <c r="R46" t="n">
-        <v>7299138</v>
+        <v>7298882</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088850</v>
+        <v>120088828</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777502</v>
+        <v>777455</v>
       </c>
       <c r="R3" t="n">
-        <v>7298806</v>
+        <v>7298795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088867</v>
+        <v>120088856</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -923,17 +923,13 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777364</v>
+        <v>777378</v>
       </c>
       <c r="R4" t="n">
         <v>7298811</v>
@@ -977,7 +973,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -989,17 +984,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088843</v>
+        <v>120088870</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777504</v>
+        <v>777507</v>
       </c>
       <c r="R5" t="n">
-        <v>7298945</v>
+        <v>7299148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088840</v>
+        <v>120088862</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777485</v>
+        <v>777412</v>
       </c>
       <c r="R6" t="n">
-        <v>7299147</v>
+        <v>7298815</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088841</v>
+        <v>120088854</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777505</v>
+        <v>777398</v>
       </c>
       <c r="R7" t="n">
-        <v>7299152</v>
+        <v>7298832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088854</v>
+        <v>120088858</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777398</v>
+        <v>777356</v>
       </c>
       <c r="R8" t="n">
-        <v>7298832</v>
+        <v>7298837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088828</v>
+        <v>120088831</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>79652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777455</v>
+        <v>777532</v>
       </c>
       <c r="R9" t="n">
-        <v>7298795</v>
+        <v>7299086</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088855</v>
+        <v>120088829</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777392</v>
+        <v>777417</v>
       </c>
       <c r="R10" t="n">
-        <v>7298835</v>
+        <v>7298838</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,37 +1603,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088868</v>
+        <v>120088845</v>
       </c>
       <c r="B11" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777492</v>
+        <v>777508</v>
       </c>
       <c r="R11" t="n">
-        <v>7299157</v>
+        <v>7298912</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088870</v>
+        <v>120088852</v>
       </c>
       <c r="B12" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777507</v>
+        <v>777427</v>
       </c>
       <c r="R12" t="n">
-        <v>7299148</v>
+        <v>7298810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088834</v>
+        <v>120088866</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,38 +1819,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777529</v>
+        <v>777389</v>
       </c>
       <c r="R13" t="n">
-        <v>7299081</v>
+        <v>7298847</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,6 +1895,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1907,14 +1907,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088866</v>
+        <v>120088855</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1948,20 +1948,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777389</v>
+        <v>777392</v>
       </c>
       <c r="R14" t="n">
-        <v>7298847</v>
+        <v>7298835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,7 +1998,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2014,14 +2009,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088856</v>
+        <v>120088857</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777378</v>
+        <v>777367</v>
       </c>
       <c r="R15" t="n">
-        <v>7298811</v>
+        <v>7298814</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,37 +2118,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088851</v>
+        <v>120088868</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777457</v>
+        <v>777492</v>
       </c>
       <c r="R16" t="n">
-        <v>7298804</v>
+        <v>7299157</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088862</v>
+        <v>120088863</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777412</v>
+        <v>777515</v>
       </c>
       <c r="R17" t="n">
-        <v>7298815</v>
+        <v>7299124</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088849</v>
+        <v>120088865</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2361,16 +2356,20 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777511</v>
+        <v>777415</v>
       </c>
       <c r="R18" t="n">
-        <v>7298804</v>
+        <v>7298849</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,6 +2410,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088869</v>
+        <v>120088840</v>
       </c>
       <c r="B19" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777505</v>
+        <v>777485</v>
       </c>
       <c r="R19" t="n">
-        <v>7299155</v>
+        <v>7299147</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088845</v>
+        <v>120088851</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777508</v>
+        <v>777457</v>
       </c>
       <c r="R20" t="n">
-        <v>7298912</v>
+        <v>7298804</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088846</v>
+        <v>120088847</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777509</v>
+        <v>777517</v>
       </c>
       <c r="R21" t="n">
-        <v>7298862</v>
+        <v>7298828</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088847</v>
+        <v>120088864</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2747,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777517</v>
+        <v>777355</v>
       </c>
       <c r="R22" t="n">
-        <v>7298828</v>
+        <v>7298843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088827</v>
+        <v>120088842</v>
       </c>
       <c r="B23" t="n">
-        <v>87423</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777473</v>
+        <v>777507</v>
       </c>
       <c r="R23" t="n">
-        <v>7298817</v>
+        <v>7299126</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088831</v>
+        <v>120088834</v>
       </c>
       <c r="B24" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777532</v>
+        <v>777529</v>
       </c>
       <c r="R24" t="n">
-        <v>7299086</v>
+        <v>7299081</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088852</v>
+        <v>120088843</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777427</v>
+        <v>777504</v>
       </c>
       <c r="R25" t="n">
-        <v>7298810</v>
+        <v>7298945</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088865</v>
+        <v>120088867</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777415</v>
+        <v>777364</v>
       </c>
       <c r="R26" t="n">
-        <v>7298849</v>
+        <v>7298811</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088857</v>
+        <v>120088827</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>87423</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777367</v>
+        <v>777473</v>
       </c>
       <c r="R27" t="n">
-        <v>7298814</v>
+        <v>7298817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088858</v>
+        <v>120088841</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777356</v>
+        <v>777505</v>
       </c>
       <c r="R28" t="n">
-        <v>7298837</v>
+        <v>7299152</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088863</v>
+        <v>120088849</v>
       </c>
       <c r="B29" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,25 +3466,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777515</v>
+        <v>777511</v>
       </c>
       <c r="R29" t="n">
-        <v>7299124</v>
+        <v>7298804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088853</v>
+        <v>120088846</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777429</v>
+        <v>777509</v>
       </c>
       <c r="R30" t="n">
-        <v>7298824</v>
+        <v>7298862</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088864</v>
+        <v>120088850</v>
       </c>
       <c r="B31" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777355</v>
+        <v>777502</v>
       </c>
       <c r="R31" t="n">
-        <v>7298843</v>
+        <v>7298806</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088829</v>
+        <v>120088853</v>
       </c>
       <c r="B32" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,25 +3772,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777417</v>
+        <v>777429</v>
       </c>
       <c r="R32" t="n">
-        <v>7298838</v>
+        <v>7298824</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088842</v>
+        <v>120088869</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777507</v>
+        <v>777505</v>
       </c>
       <c r="R33" t="n">
-        <v>7299126</v>
+        <v>7299155</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109450</v>
+        <v>120109443</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777403</v>
+        <v>777444</v>
       </c>
       <c r="R34" t="n">
-        <v>7298895</v>
+        <v>7298925</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109445</v>
+        <v>120109457</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777555</v>
+        <v>777600</v>
       </c>
       <c r="R35" t="n">
-        <v>7299109</v>
+        <v>7299114</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109449</v>
+        <v>120109450</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777456</v>
+        <v>777403</v>
       </c>
       <c r="R36" t="n">
-        <v>7298953</v>
+        <v>7298895</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109452</v>
+        <v>120109444</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777449</v>
+        <v>777573</v>
       </c>
       <c r="R37" t="n">
-        <v>7298879</v>
+        <v>7299187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109443</v>
+        <v>120109447</v>
       </c>
       <c r="B38" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777444</v>
+        <v>777398</v>
       </c>
       <c r="R38" t="n">
-        <v>7298925</v>
+        <v>7298959</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109444</v>
+        <v>120109453</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777573</v>
+        <v>777456</v>
       </c>
       <c r="R39" t="n">
-        <v>7299187</v>
+        <v>7298884</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109457</v>
+        <v>120109454</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777600</v>
+        <v>777458</v>
       </c>
       <c r="R40" t="n">
-        <v>7299114</v>
+        <v>7298865</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109459</v>
+        <v>120109449</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777599</v>
+        <v>777456</v>
       </c>
       <c r="R41" t="n">
-        <v>7299147</v>
+        <v>7298953</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109446</v>
+        <v>120109465</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4792,25 +4792,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777434</v>
+        <v>777595</v>
       </c>
       <c r="R42" t="n">
-        <v>7298954</v>
+        <v>7299138</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109447</v>
+        <v>120109455</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777398</v>
+        <v>777511</v>
       </c>
       <c r="R43" t="n">
-        <v>7298959</v>
+        <v>7298851</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109465</v>
+        <v>120109459</v>
       </c>
       <c r="B44" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4996,25 +4996,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777595</v>
+        <v>777599</v>
       </c>
       <c r="R44" t="n">
-        <v>7299138</v>
+        <v>7299147</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109448</v>
+        <v>120109445</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777417</v>
+        <v>777555</v>
       </c>
       <c r="R45" t="n">
-        <v>7298952</v>
+        <v>7299109</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109455</v>
+        <v>120109448</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777511</v>
+        <v>777417</v>
       </c>
       <c r="R47" t="n">
-        <v>7298851</v>
+        <v>7298952</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109454</v>
+        <v>120109446</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777458</v>
+        <v>777434</v>
       </c>
       <c r="R48" t="n">
-        <v>7298865</v>
+        <v>7298954</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109453</v>
+        <v>120109452</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777456</v>
+        <v>777449</v>
       </c>
       <c r="R49" t="n">
-        <v>7298884</v>
+        <v>7298879</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1603,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088845</v>
+        <v>120088855</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777508</v>
+        <v>777392</v>
       </c>
       <c r="R11" t="n">
-        <v>7298912</v>
+        <v>7298835</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088852</v>
+        <v>120088845</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777427</v>
+        <v>777508</v>
       </c>
       <c r="R12" t="n">
-        <v>7298810</v>
+        <v>7298912</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088866</v>
+        <v>120088852</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1841,20 +1841,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777389</v>
+        <v>777427</v>
       </c>
       <c r="R13" t="n">
-        <v>7298847</v>
+        <v>7298810</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,7 +1891,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1907,14 +1902,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088855</v>
+        <v>120088866</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1948,16 +1943,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777392</v>
+        <v>777389</v>
       </c>
       <c r="R14" t="n">
-        <v>7298835</v>
+        <v>7298847</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +1997,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2118,37 +2118,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088868</v>
+        <v>120088863</v>
       </c>
       <c r="B16" t="n">
-        <v>95225</v>
+        <v>82321</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777492</v>
+        <v>777515</v>
       </c>
       <c r="R16" t="n">
-        <v>7299157</v>
+        <v>7299124</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088863</v>
+        <v>120088865</v>
       </c>
       <c r="B17" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,38 +2232,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777515</v>
+        <v>777415</v>
       </c>
       <c r="R17" t="n">
-        <v>7299124</v>
+        <v>7298849</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,6 +2308,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2315,14 +2320,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088865</v>
+        <v>120088840</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2356,20 +2361,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777415</v>
+        <v>777485</v>
       </c>
       <c r="R18" t="n">
-        <v>7298849</v>
+        <v>7299147</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2411,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2422,14 +2422,14 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088840</v>
+        <v>120088851</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777485</v>
+        <v>777457</v>
       </c>
       <c r="R19" t="n">
-        <v>7299147</v>
+        <v>7298804</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,37 +2531,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088851</v>
+        <v>120088868</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777457</v>
+        <v>777492</v>
       </c>
       <c r="R20" t="n">
-        <v>7298804</v>
+        <v>7299157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088834</v>
+        <v>120088843</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777529</v>
+        <v>777504</v>
       </c>
       <c r="R24" t="n">
-        <v>7299081</v>
+        <v>7298945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088843</v>
+        <v>120088867</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3075,16 +3075,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777504</v>
+        <v>777364</v>
       </c>
       <c r="R25" t="n">
-        <v>7298945</v>
+        <v>7298811</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,6 +3129,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3136,17 +3141,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088867</v>
+        <v>120088834</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,42 +3160,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777364</v>
+        <v>777529</v>
       </c>
       <c r="R26" t="n">
-        <v>7298811</v>
+        <v>7299081</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3231,7 +3232,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088828</v>
+        <v>120088831</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777455</v>
+        <v>777532</v>
       </c>
       <c r="R3" t="n">
-        <v>7298795</v>
+        <v>7299086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088856</v>
+        <v>120088841</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777378</v>
+        <v>777505</v>
       </c>
       <c r="R4" t="n">
-        <v>7298811</v>
+        <v>7299152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088870</v>
+        <v>120088850</v>
       </c>
       <c r="B5" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777507</v>
+        <v>777502</v>
       </c>
       <c r="R5" t="n">
-        <v>7299148</v>
+        <v>7298806</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088862</v>
+        <v>120088869</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777412</v>
+        <v>777505</v>
       </c>
       <c r="R6" t="n">
-        <v>7298815</v>
+        <v>7299155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088854</v>
+        <v>120088849</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777398</v>
+        <v>777511</v>
       </c>
       <c r="R7" t="n">
-        <v>7298832</v>
+        <v>7298804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088858</v>
+        <v>120088840</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777356</v>
+        <v>777485</v>
       </c>
       <c r="R8" t="n">
-        <v>7298837</v>
+        <v>7299147</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088831</v>
+        <v>120088855</v>
       </c>
       <c r="B9" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777532</v>
+        <v>777392</v>
       </c>
       <c r="R9" t="n">
-        <v>7299086</v>
+        <v>7298835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088829</v>
+        <v>120088853</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777417</v>
+        <v>777429</v>
       </c>
       <c r="R10" t="n">
-        <v>7298838</v>
+        <v>7298824</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088855</v>
+        <v>120088870</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777392</v>
+        <v>777507</v>
       </c>
       <c r="R11" t="n">
-        <v>7298835</v>
+        <v>7299148</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088845</v>
+        <v>120088843</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777508</v>
+        <v>777504</v>
       </c>
       <c r="R12" t="n">
-        <v>7298912</v>
+        <v>7298945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088852</v>
+        <v>120088867</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1841,16 +1841,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777427</v>
+        <v>777364</v>
       </c>
       <c r="R13" t="n">
-        <v>7298810</v>
+        <v>7298811</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1891,6 +1895,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1902,17 +1907,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088866</v>
+        <v>120088828</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,42 +1926,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777389</v>
+        <v>777455</v>
       </c>
       <c r="R14" t="n">
-        <v>7298847</v>
+        <v>7298795</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,7 +1998,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088857</v>
+        <v>120088854</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777367</v>
+        <v>777398</v>
       </c>
       <c r="R15" t="n">
-        <v>7298814</v>
+        <v>7298832</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088863</v>
+        <v>120088866</v>
       </c>
       <c r="B16" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,38 +2130,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777515</v>
+        <v>777389</v>
       </c>
       <c r="R16" t="n">
-        <v>7299124</v>
+        <v>7298847</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2202,6 +2206,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2213,14 +2218,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088865</v>
+        <v>120088858</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2254,20 +2259,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777415</v>
+        <v>777356</v>
       </c>
       <c r="R17" t="n">
-        <v>7298849</v>
+        <v>7298837</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,7 +2309,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,14 +2320,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088840</v>
+        <v>120088847</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777485</v>
+        <v>777517</v>
       </c>
       <c r="R18" t="n">
-        <v>7299147</v>
+        <v>7298828</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088851</v>
+        <v>120088857</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777457</v>
+        <v>777367</v>
       </c>
       <c r="R19" t="n">
-        <v>7298804</v>
+        <v>7298814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,37 +2531,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088868</v>
+        <v>120088834</v>
       </c>
       <c r="B20" t="n">
-        <v>95225</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777492</v>
+        <v>777529</v>
       </c>
       <c r="R20" t="n">
-        <v>7299157</v>
+        <v>7299081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,37 +2633,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088847</v>
+        <v>120088868</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777517</v>
+        <v>777492</v>
       </c>
       <c r="R21" t="n">
-        <v>7298828</v>
+        <v>7299157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088864</v>
+        <v>120088865</v>
       </c>
       <c r="B22" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,38 +2747,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777355</v>
+        <v>777415</v>
       </c>
       <c r="R22" t="n">
-        <v>7298843</v>
+        <v>7298849</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2823,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2830,14 +2835,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088842</v>
+        <v>120088851</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -2877,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777507</v>
+        <v>777457</v>
       </c>
       <c r="R23" t="n">
-        <v>7299126</v>
+        <v>7298804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,7 +2944,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088843</v>
+        <v>120088846</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777504</v>
+        <v>777509</v>
       </c>
       <c r="R24" t="n">
-        <v>7298945</v>
+        <v>7298862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3046,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088867</v>
+        <v>120088864</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,42 +3058,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777364</v>
+        <v>777355</v>
       </c>
       <c r="R25" t="n">
-        <v>7298811</v>
+        <v>7298843</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,7 +3130,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3141,17 +3141,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088834</v>
+        <v>120088863</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>82321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777529</v>
+        <v>777515</v>
       </c>
       <c r="R26" t="n">
-        <v>7299081</v>
+        <v>7299124</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088827</v>
+        <v>120088829</v>
       </c>
       <c r="B27" t="n">
-        <v>87423</v>
+        <v>90545</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777473</v>
+        <v>777417</v>
       </c>
       <c r="R27" t="n">
-        <v>7298817</v>
+        <v>7298838</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088841</v>
+        <v>120088827</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>87423</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777505</v>
+        <v>777473</v>
       </c>
       <c r="R28" t="n">
-        <v>7299152</v>
+        <v>7298817</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088849</v>
+        <v>120088856</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3494,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777511</v>
+        <v>777378</v>
       </c>
       <c r="R29" t="n">
-        <v>7298804</v>
+        <v>7298811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088846</v>
+        <v>120088842</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777509</v>
+        <v>777507</v>
       </c>
       <c r="R30" t="n">
-        <v>7298862</v>
+        <v>7299126</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088850</v>
+        <v>120088845</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777502</v>
+        <v>777508</v>
       </c>
       <c r="R31" t="n">
-        <v>7298806</v>
+        <v>7298912</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088853</v>
+        <v>120088852</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777429</v>
+        <v>777427</v>
       </c>
       <c r="R32" t="n">
-        <v>7298824</v>
+        <v>7298810</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088869</v>
+        <v>120088862</v>
       </c>
       <c r="B33" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777505</v>
+        <v>777412</v>
       </c>
       <c r="R33" t="n">
-        <v>7299155</v>
+        <v>7298815</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109443</v>
+        <v>120109465</v>
       </c>
       <c r="B34" t="n">
-        <v>96891</v>
+        <v>82321</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777444</v>
+        <v>777595</v>
       </c>
       <c r="R34" t="n">
-        <v>7298925</v>
+        <v>7299138</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109457</v>
+        <v>120109446</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777600</v>
+        <v>777434</v>
       </c>
       <c r="R35" t="n">
-        <v>7299114</v>
+        <v>7298954</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109450</v>
+        <v>120109451</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777403</v>
+        <v>777444</v>
       </c>
       <c r="R36" t="n">
-        <v>7298895</v>
+        <v>7298882</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109444</v>
+        <v>120109453</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777573</v>
+        <v>777456</v>
       </c>
       <c r="R37" t="n">
-        <v>7299187</v>
+        <v>7298884</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109453</v>
+        <v>120109450</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777456</v>
+        <v>777403</v>
       </c>
       <c r="R39" t="n">
-        <v>7298884</v>
+        <v>7298895</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109449</v>
+        <v>120109452</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777456</v>
+        <v>777449</v>
       </c>
       <c r="R41" t="n">
-        <v>7298953</v>
+        <v>7298879</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109465</v>
+        <v>120109448</v>
       </c>
       <c r="B42" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4792,25 +4792,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777595</v>
+        <v>777417</v>
       </c>
       <c r="R42" t="n">
-        <v>7299138</v>
+        <v>7298952</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109455</v>
+        <v>120109445</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777511</v>
+        <v>777555</v>
       </c>
       <c r="R43" t="n">
-        <v>7298851</v>
+        <v>7299109</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109459</v>
+        <v>120109457</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777599</v>
+        <v>777600</v>
       </c>
       <c r="R44" t="n">
-        <v>7299147</v>
+        <v>7299114</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109445</v>
+        <v>120109459</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777555</v>
+        <v>777599</v>
       </c>
       <c r="R45" t="n">
-        <v>7299109</v>
+        <v>7299147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109451</v>
+        <v>120109449</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777444</v>
+        <v>777456</v>
       </c>
       <c r="R46" t="n">
-        <v>7298882</v>
+        <v>7298953</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109448</v>
+        <v>120109455</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777417</v>
+        <v>777511</v>
       </c>
       <c r="R47" t="n">
-        <v>7298952</v>
+        <v>7298851</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109446</v>
+        <v>120109444</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777434</v>
+        <v>777573</v>
       </c>
       <c r="R48" t="n">
-        <v>7298954</v>
+        <v>7299187</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109452</v>
+        <v>120109443</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5506,25 +5506,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777449</v>
+        <v>777444</v>
       </c>
       <c r="R49" t="n">
-        <v>7298879</v>
+        <v>7298925</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088867</v>
+        <v>120088828</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,42 +1819,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777364</v>
+        <v>777455</v>
       </c>
       <c r="R13" t="n">
-        <v>7298811</v>
+        <v>7298795</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,7 +1891,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1907,17 +1902,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088828</v>
+        <v>120088867</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,38 +1921,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777455</v>
+        <v>777364</v>
       </c>
       <c r="R14" t="n">
-        <v>7298795</v>
+        <v>7298811</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +1997,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088847</v>
+        <v>120088857</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777517</v>
+        <v>777367</v>
       </c>
       <c r="R18" t="n">
-        <v>7298828</v>
+        <v>7298814</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088857</v>
+        <v>120088847</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777367</v>
+        <v>777517</v>
       </c>
       <c r="R19" t="n">
-        <v>7298814</v>
+        <v>7298828</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088865</v>
+        <v>120088846</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2769,20 +2769,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777415</v>
+        <v>777509</v>
       </c>
       <c r="R22" t="n">
-        <v>7298849</v>
+        <v>7298862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,7 +2819,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2835,14 +2830,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088851</v>
+        <v>120088865</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -2876,16 +2871,20 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777457</v>
+        <v>777415</v>
       </c>
       <c r="R23" t="n">
-        <v>7298804</v>
+        <v>7298849</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,6 +2925,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2937,14 +2937,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088846</v>
+        <v>120088851</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777509</v>
+        <v>777457</v>
       </c>
       <c r="R24" t="n">
-        <v>7298862</v>
+        <v>7298804</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088845</v>
+        <v>120088862</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3670,25 +3670,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777508</v>
+        <v>777412</v>
       </c>
       <c r="R31" t="n">
-        <v>7298912</v>
+        <v>7298815</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088852</v>
+        <v>120088845</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777427</v>
+        <v>777508</v>
       </c>
       <c r="R32" t="n">
-        <v>7298810</v>
+        <v>7298912</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088862</v>
+        <v>120088852</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777412</v>
+        <v>777427</v>
       </c>
       <c r="R33" t="n">
-        <v>7298815</v>
+        <v>7298810</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088831</v>
+        <v>120088849</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777532</v>
+        <v>777511</v>
       </c>
       <c r="R3" t="n">
-        <v>7299086</v>
+        <v>7298804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088841</v>
+        <v>120088828</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777505</v>
+        <v>777455</v>
       </c>
       <c r="R4" t="n">
-        <v>7299152</v>
+        <v>7298795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088850</v>
+        <v>120088840</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777502</v>
+        <v>777485</v>
       </c>
       <c r="R5" t="n">
-        <v>7298806</v>
+        <v>7299147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088849</v>
+        <v>120088867</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1229,16 +1229,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777511</v>
+        <v>777364</v>
       </c>
       <c r="R7" t="n">
-        <v>7298804</v>
+        <v>7298811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,6 +1283,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,14 +1295,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088840</v>
+        <v>120088842</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777485</v>
+        <v>777507</v>
       </c>
       <c r="R8" t="n">
-        <v>7299147</v>
+        <v>7299126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088855</v>
+        <v>120088856</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777392</v>
+        <v>777378</v>
       </c>
       <c r="R9" t="n">
-        <v>7298835</v>
+        <v>7298811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088853</v>
+        <v>120088845</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777429</v>
+        <v>777508</v>
       </c>
       <c r="R10" t="n">
-        <v>7298824</v>
+        <v>7298912</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088870</v>
+        <v>120088850</v>
       </c>
       <c r="B11" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777507</v>
+        <v>777502</v>
       </c>
       <c r="R11" t="n">
-        <v>7299148</v>
+        <v>7298806</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088843</v>
+        <v>120088857</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1745,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777504</v>
+        <v>777367</v>
       </c>
       <c r="R12" t="n">
-        <v>7298945</v>
+        <v>7298814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088828</v>
+        <v>120088853</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777455</v>
+        <v>777429</v>
       </c>
       <c r="R13" t="n">
-        <v>7298795</v>
+        <v>7298824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088867</v>
+        <v>120088847</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1943,20 +1948,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777364</v>
+        <v>777517</v>
       </c>
       <c r="R14" t="n">
-        <v>7298811</v>
+        <v>7298828</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,7 +1998,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088854</v>
+        <v>120088841</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777398</v>
+        <v>777505</v>
       </c>
       <c r="R15" t="n">
-        <v>7298832</v>
+        <v>7299152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088858</v>
+        <v>120088855</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777356</v>
+        <v>777392</v>
       </c>
       <c r="R17" t="n">
-        <v>7298837</v>
+        <v>7298835</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088857</v>
+        <v>120088858</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777367</v>
+        <v>777356</v>
       </c>
       <c r="R18" t="n">
-        <v>7298814</v>
+        <v>7298837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088847</v>
+        <v>120088864</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777517</v>
+        <v>777355</v>
       </c>
       <c r="R19" t="n">
-        <v>7298828</v>
+        <v>7298843</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,14 +2633,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088868</v>
+        <v>120088829</v>
       </c>
       <c r="B21" t="n">
-        <v>95225</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2649,21 +2649,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777492</v>
+        <v>777417</v>
       </c>
       <c r="R21" t="n">
-        <v>7299157</v>
+        <v>7298838</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088846</v>
+        <v>120088862</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2747,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777509</v>
+        <v>777412</v>
       </c>
       <c r="R22" t="n">
-        <v>7298862</v>
+        <v>7298815</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088865</v>
+        <v>120088852</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -2871,20 +2871,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777415</v>
+        <v>777427</v>
       </c>
       <c r="R23" t="n">
-        <v>7298849</v>
+        <v>7298810</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2921,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2937,17 +2932,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088851</v>
+        <v>120088863</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777457</v>
+        <v>777515</v>
       </c>
       <c r="R24" t="n">
-        <v>7298804</v>
+        <v>7299124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088864</v>
+        <v>120088831</v>
       </c>
       <c r="B25" t="n">
-        <v>82321</v>
+        <v>79652</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3053,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777355</v>
+        <v>777532</v>
       </c>
       <c r="R25" t="n">
-        <v>7298843</v>
+        <v>7299086</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,10 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088863</v>
+        <v>120088851</v>
       </c>
       <c r="B26" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3155,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777515</v>
+        <v>777457</v>
       </c>
       <c r="R26" t="n">
-        <v>7299124</v>
+        <v>7298804</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088829</v>
+        <v>120088827</v>
       </c>
       <c r="B27" t="n">
-        <v>90545</v>
+        <v>87423</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3257,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777417</v>
+        <v>777473</v>
       </c>
       <c r="R27" t="n">
-        <v>7298838</v>
+        <v>7298817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088827</v>
+        <v>120088870</v>
       </c>
       <c r="B28" t="n">
-        <v>87423</v>
+        <v>95225</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3359,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4412</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777473</v>
+        <v>777507</v>
       </c>
       <c r="R28" t="n">
-        <v>7298817</v>
+        <v>7299148</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,7 +3449,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088856</v>
+        <v>120088843</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3494,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777378</v>
+        <v>777504</v>
       </c>
       <c r="R29" t="n">
-        <v>7298811</v>
+        <v>7298945</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3551,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088842</v>
+        <v>120088854</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3596,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777507</v>
+        <v>777398</v>
       </c>
       <c r="R30" t="n">
-        <v>7299126</v>
+        <v>7298832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,37 +3653,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088862</v>
+        <v>120088868</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777412</v>
+        <v>777492</v>
       </c>
       <c r="R31" t="n">
-        <v>7298815</v>
+        <v>7299157</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,7 +3755,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088845</v>
+        <v>120088865</v>
       </c>
       <c r="B32" t="n">
         <v>97930</v>
@@ -3794,16 +3789,20 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777508</v>
+        <v>777415</v>
       </c>
       <c r="R32" t="n">
-        <v>7298912</v>
+        <v>7298849</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,6 +3843,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3855,14 +3855,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088852</v>
+        <v>120088846</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777427</v>
+        <v>777509</v>
       </c>
       <c r="R33" t="n">
-        <v>7298810</v>
+        <v>7298862</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109465</v>
+        <v>120109450</v>
       </c>
       <c r="B34" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,25 +3976,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777595</v>
+        <v>777403</v>
       </c>
       <c r="R34" t="n">
-        <v>7299138</v>
+        <v>7298895</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109446</v>
+        <v>120109465</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4078,25 +4078,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777434</v>
+        <v>777595</v>
       </c>
       <c r="R35" t="n">
-        <v>7298954</v>
+        <v>7299138</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109451</v>
+        <v>120109443</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4180,25 +4180,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4211,7 +4211,7 @@
         <v>777444</v>
       </c>
       <c r="R36" t="n">
-        <v>7298882</v>
+        <v>7298925</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109453</v>
+        <v>120109449</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4313,7 +4313,7 @@
         <v>777456</v>
       </c>
       <c r="R37" t="n">
-        <v>7298884</v>
+        <v>7298953</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109447</v>
+        <v>120109453</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777398</v>
+        <v>777456</v>
       </c>
       <c r="R38" t="n">
-        <v>7298959</v>
+        <v>7298884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109450</v>
+        <v>120109445</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777403</v>
+        <v>777555</v>
       </c>
       <c r="R39" t="n">
-        <v>7298895</v>
+        <v>7299109</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109454</v>
+        <v>120109452</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777458</v>
+        <v>777449</v>
       </c>
       <c r="R40" t="n">
-        <v>7298865</v>
+        <v>7298879</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109452</v>
+        <v>120109457</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777449</v>
+        <v>777600</v>
       </c>
       <c r="R41" t="n">
-        <v>7298879</v>
+        <v>7299114</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109448</v>
+        <v>120109459</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777417</v>
+        <v>777599</v>
       </c>
       <c r="R42" t="n">
-        <v>7298952</v>
+        <v>7299147</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109445</v>
+        <v>120109447</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777555</v>
+        <v>777398</v>
       </c>
       <c r="R43" t="n">
-        <v>7299109</v>
+        <v>7298959</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109457</v>
+        <v>120109446</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777600</v>
+        <v>777434</v>
       </c>
       <c r="R44" t="n">
-        <v>7299114</v>
+        <v>7298954</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109459</v>
+        <v>120109454</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777599</v>
+        <v>777458</v>
       </c>
       <c r="R45" t="n">
-        <v>7299147</v>
+        <v>7298865</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109449</v>
+        <v>120109444</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777456</v>
+        <v>777573</v>
       </c>
       <c r="R46" t="n">
-        <v>7298953</v>
+        <v>7299187</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109444</v>
+        <v>120109451</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777573</v>
+        <v>777444</v>
       </c>
       <c r="R48" t="n">
-        <v>7299187</v>
+        <v>7298882</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109443</v>
+        <v>120109448</v>
       </c>
       <c r="B49" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5506,25 +5506,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777444</v>
+        <v>777417</v>
       </c>
       <c r="R49" t="n">
-        <v>7298925</v>
+        <v>7298952</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088849</v>
+        <v>120088853</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777511</v>
+        <v>777429</v>
       </c>
       <c r="R3" t="n">
-        <v>7298804</v>
+        <v>7298824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088828</v>
+        <v>120088847</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777455</v>
+        <v>777517</v>
       </c>
       <c r="R4" t="n">
-        <v>7298795</v>
+        <v>7298828</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088840</v>
+        <v>120088851</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777485</v>
+        <v>777457</v>
       </c>
       <c r="R5" t="n">
-        <v>7299147</v>
+        <v>7298804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088869</v>
+        <v>120088849</v>
       </c>
       <c r="B6" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777505</v>
+        <v>777511</v>
       </c>
       <c r="R6" t="n">
-        <v>7299155</v>
+        <v>7298804</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088867</v>
+        <v>120088869</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,42 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777364</v>
+        <v>777505</v>
       </c>
       <c r="R7" t="n">
-        <v>7298811</v>
+        <v>7299155</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1279,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,14 +1290,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088842</v>
+        <v>120088854</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777507</v>
+        <v>777398</v>
       </c>
       <c r="R8" t="n">
-        <v>7299126</v>
+        <v>7298832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088856</v>
+        <v>120088840</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777378</v>
+        <v>777485</v>
       </c>
       <c r="R9" t="n">
-        <v>7298811</v>
+        <v>7299147</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088845</v>
+        <v>120088846</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777508</v>
+        <v>777509</v>
       </c>
       <c r="R10" t="n">
-        <v>7298912</v>
+        <v>7298862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088857</v>
+        <v>120088863</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777367</v>
+        <v>777515</v>
       </c>
       <c r="R12" t="n">
-        <v>7298814</v>
+        <v>7299124</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088853</v>
+        <v>120088829</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777429</v>
+        <v>777417</v>
       </c>
       <c r="R13" t="n">
-        <v>7298824</v>
+        <v>7298838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088847</v>
+        <v>120088866</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -1948,16 +1943,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777517</v>
+        <v>777389</v>
       </c>
       <c r="R14" t="n">
-        <v>7298828</v>
+        <v>7298847</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +1997,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088841</v>
+        <v>120088845</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777505</v>
+        <v>777508</v>
       </c>
       <c r="R15" t="n">
-        <v>7299152</v>
+        <v>7298912</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088866</v>
+        <v>120088843</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2152,20 +2152,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777389</v>
+        <v>777504</v>
       </c>
       <c r="R16" t="n">
-        <v>7298847</v>
+        <v>7298945</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,7 +2202,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2218,14 +2213,14 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088855</v>
+        <v>120088852</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777392</v>
+        <v>777427</v>
       </c>
       <c r="R17" t="n">
-        <v>7298835</v>
+        <v>7298810</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088858</v>
+        <v>120088870</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777356</v>
+        <v>777507</v>
       </c>
       <c r="R18" t="n">
-        <v>7298837</v>
+        <v>7299148</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088864</v>
+        <v>120088831</v>
       </c>
       <c r="B19" t="n">
-        <v>82321</v>
+        <v>79652</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2436,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777355</v>
+        <v>777532</v>
       </c>
       <c r="R19" t="n">
-        <v>7298843</v>
+        <v>7299086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088834</v>
+        <v>120088865</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,38 +2538,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777529</v>
+        <v>777415</v>
       </c>
       <c r="R20" t="n">
-        <v>7299081</v>
+        <v>7298849</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,6 +2614,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,17 +2626,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088829</v>
+        <v>120088864</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>82321</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777417</v>
+        <v>777355</v>
       </c>
       <c r="R21" t="n">
-        <v>7298838</v>
+        <v>7298843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088862</v>
+        <v>120088828</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777412</v>
+        <v>777455</v>
       </c>
       <c r="R22" t="n">
-        <v>7298815</v>
+        <v>7298795</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088852</v>
+        <v>120088834</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2849,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777427</v>
+        <v>777529</v>
       </c>
       <c r="R23" t="n">
-        <v>7298810</v>
+        <v>7299081</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088863</v>
+        <v>120088862</v>
       </c>
       <c r="B24" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777515</v>
+        <v>777412</v>
       </c>
       <c r="R24" t="n">
-        <v>7299124</v>
+        <v>7298815</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088831</v>
+        <v>120088841</v>
       </c>
       <c r="B25" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,25 +3053,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777532</v>
+        <v>777505</v>
       </c>
       <c r="R25" t="n">
-        <v>7299086</v>
+        <v>7299152</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088851</v>
+        <v>120088855</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777457</v>
+        <v>777392</v>
       </c>
       <c r="R26" t="n">
-        <v>7298804</v>
+        <v>7298835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088827</v>
+        <v>120088858</v>
       </c>
       <c r="B27" t="n">
-        <v>87423</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,25 +3257,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777473</v>
+        <v>777356</v>
       </c>
       <c r="R27" t="n">
-        <v>7298817</v>
+        <v>7298837</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088870</v>
+        <v>120088867</v>
       </c>
       <c r="B28" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,38 +3359,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777507</v>
+        <v>777364</v>
       </c>
       <c r="R28" t="n">
-        <v>7299148</v>
+        <v>7298811</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,6 +3435,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3442,14 +3447,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088843</v>
+        <v>120088842</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3489,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777504</v>
+        <v>777507</v>
       </c>
       <c r="R29" t="n">
-        <v>7298945</v>
+        <v>7299126</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088854</v>
+        <v>120088856</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3591,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777398</v>
+        <v>777378</v>
       </c>
       <c r="R30" t="n">
-        <v>7298832</v>
+        <v>7298811</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3755,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088865</v>
+        <v>120088827</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>87423</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3767,42 +3772,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777415</v>
+        <v>777473</v>
       </c>
       <c r="R32" t="n">
-        <v>7298849</v>
+        <v>7298817</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3843,7 +3844,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3855,14 +3855,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088846</v>
+        <v>120088857</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777509</v>
+        <v>777367</v>
       </c>
       <c r="R33" t="n">
-        <v>7298862</v>
+        <v>7298814</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109450</v>
+        <v>120109444</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777403</v>
+        <v>777573</v>
       </c>
       <c r="R34" t="n">
-        <v>7298895</v>
+        <v>7299187</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109465</v>
+        <v>120109452</v>
       </c>
       <c r="B35" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4078,25 +4078,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777595</v>
+        <v>777449</v>
       </c>
       <c r="R35" t="n">
-        <v>7299138</v>
+        <v>7298879</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109443</v>
+        <v>120109448</v>
       </c>
       <c r="B36" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4180,25 +4180,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777444</v>
+        <v>777417</v>
       </c>
       <c r="R36" t="n">
-        <v>7298925</v>
+        <v>7298952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109449</v>
+        <v>120109445</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777456</v>
+        <v>777555</v>
       </c>
       <c r="R37" t="n">
-        <v>7298953</v>
+        <v>7299109</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109453</v>
+        <v>120109457</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777456</v>
+        <v>777600</v>
       </c>
       <c r="R38" t="n">
-        <v>7298884</v>
+        <v>7299114</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109445</v>
+        <v>120109449</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777555</v>
+        <v>777456</v>
       </c>
       <c r="R39" t="n">
-        <v>7299109</v>
+        <v>7298953</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,7 +4576,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109452</v>
+        <v>120109455</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777449</v>
+        <v>777511</v>
       </c>
       <c r="R40" t="n">
-        <v>7298879</v>
+        <v>7298851</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109457</v>
+        <v>120109446</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777600</v>
+        <v>777434</v>
       </c>
       <c r="R41" t="n">
-        <v>7299114</v>
+        <v>7298954</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109459</v>
+        <v>120109465</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4792,25 +4792,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777599</v>
+        <v>777595</v>
       </c>
       <c r="R42" t="n">
-        <v>7299147</v>
+        <v>7299138</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109447</v>
+        <v>120109454</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777398</v>
+        <v>777458</v>
       </c>
       <c r="R43" t="n">
-        <v>7298959</v>
+        <v>7298865</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109446</v>
+        <v>120109459</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777434</v>
+        <v>777599</v>
       </c>
       <c r="R44" t="n">
-        <v>7298954</v>
+        <v>7299147</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109454</v>
+        <v>120109443</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5098,25 +5098,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777458</v>
+        <v>777444</v>
       </c>
       <c r="R45" t="n">
-        <v>7298865</v>
+        <v>7298925</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109444</v>
+        <v>120109450</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777573</v>
+        <v>777403</v>
       </c>
       <c r="R46" t="n">
-        <v>7299187</v>
+        <v>7298895</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109455</v>
+        <v>120109447</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777511</v>
+        <v>777398</v>
       </c>
       <c r="R47" t="n">
-        <v>7298851</v>
+        <v>7298959</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109451</v>
+        <v>120109453</v>
       </c>
       <c r="B48" t="n">
         <v>97930</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777444</v>
+        <v>777456</v>
       </c>
       <c r="R48" t="n">
-        <v>7298882</v>
+        <v>7298884</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,7 +5494,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109448</v>
+        <v>120109451</v>
       </c>
       <c r="B49" t="n">
         <v>97930</v>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777417</v>
+        <v>777444</v>
       </c>
       <c r="R49" t="n">
-        <v>7298952</v>
+        <v>7298882</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088849</v>
+        <v>120088869</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777511</v>
+        <v>777505</v>
       </c>
       <c r="R6" t="n">
-        <v>7298804</v>
+        <v>7299155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088869</v>
+        <v>120088849</v>
       </c>
       <c r="B7" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777505</v>
+        <v>777511</v>
       </c>
       <c r="R7" t="n">
-        <v>7299155</v>
+        <v>7298804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088845</v>
+        <v>120088870</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777508</v>
+        <v>777507</v>
       </c>
       <c r="R15" t="n">
-        <v>7298912</v>
+        <v>7299148</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088843</v>
+        <v>120088831</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777504</v>
+        <v>777532</v>
       </c>
       <c r="R16" t="n">
-        <v>7298945</v>
+        <v>7299086</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088852</v>
+        <v>120088845</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777427</v>
+        <v>777508</v>
       </c>
       <c r="R17" t="n">
-        <v>7298810</v>
+        <v>7298912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088870</v>
+        <v>120088843</v>
       </c>
       <c r="B18" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2334,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777507</v>
+        <v>777504</v>
       </c>
       <c r="R18" t="n">
-        <v>7299148</v>
+        <v>7298945</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088831</v>
+        <v>120088852</v>
       </c>
       <c r="B19" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2436,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777532</v>
+        <v>777427</v>
       </c>
       <c r="R19" t="n">
-        <v>7299086</v>
+        <v>7298810</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3347,54 +3347,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088867</v>
+        <v>120088868</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777364</v>
+        <v>777492</v>
       </c>
       <c r="R28" t="n">
-        <v>7298811</v>
+        <v>7299157</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,7 +3431,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3447,14 +3442,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088842</v>
+        <v>120088867</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3488,16 +3483,20 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777507</v>
+        <v>777364</v>
       </c>
       <c r="R29" t="n">
-        <v>7299126</v>
+        <v>7298811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3538,6 +3537,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3549,14 +3549,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088856</v>
+        <v>120088842</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777378</v>
+        <v>777507</v>
       </c>
       <c r="R30" t="n">
-        <v>7298811</v>
+        <v>7299126</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,37 +3658,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088868</v>
+        <v>120088856</v>
       </c>
       <c r="B31" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777492</v>
+        <v>777378</v>
       </c>
       <c r="R31" t="n">
-        <v>7299157</v>
+        <v>7298811</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088853</v>
+        <v>120088866</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -821,16 +821,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777429</v>
+        <v>777389</v>
       </c>
       <c r="R3" t="n">
-        <v>7298824</v>
+        <v>7298847</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,14 +887,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088847</v>
+        <v>120088855</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777517</v>
+        <v>777392</v>
       </c>
       <c r="R4" t="n">
-        <v>7298828</v>
+        <v>7298835</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088851</v>
+        <v>120088842</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777457</v>
+        <v>777507</v>
       </c>
       <c r="R5" t="n">
-        <v>7298804</v>
+        <v>7299126</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,14 +1098,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088869</v>
+        <v>120088868</v>
       </c>
       <c r="B6" t="n">
         <v>95225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777505</v>
+        <v>777492</v>
       </c>
       <c r="R6" t="n">
-        <v>7299155</v>
+        <v>7299157</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088849</v>
+        <v>120088867</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1229,16 +1234,20 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777511</v>
+        <v>777364</v>
       </c>
       <c r="R7" t="n">
-        <v>7298804</v>
+        <v>7298811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,6 +1288,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,17 +1300,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088854</v>
+        <v>120088869</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777398</v>
+        <v>777505</v>
       </c>
       <c r="R8" t="n">
-        <v>7298832</v>
+        <v>7299155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088840</v>
+        <v>120088845</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1439,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777485</v>
+        <v>777508</v>
       </c>
       <c r="R9" t="n">
-        <v>7299147</v>
+        <v>7298912</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088846</v>
+        <v>120088847</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1541,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777509</v>
+        <v>777517</v>
       </c>
       <c r="R10" t="n">
-        <v>7298862</v>
+        <v>7298828</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088850</v>
+        <v>120088858</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777502</v>
+        <v>777356</v>
       </c>
       <c r="R11" t="n">
-        <v>7298806</v>
+        <v>7298837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088863</v>
+        <v>120088831</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
+        <v>79652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777515</v>
+        <v>777532</v>
       </c>
       <c r="R12" t="n">
-        <v>7299124</v>
+        <v>7299086</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088829</v>
+        <v>120088827</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>87423</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777417</v>
+        <v>777473</v>
       </c>
       <c r="R13" t="n">
-        <v>7298838</v>
+        <v>7298817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088866</v>
+        <v>120088829</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,42 +1931,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777389</v>
+        <v>777417</v>
       </c>
       <c r="R14" t="n">
-        <v>7298847</v>
+        <v>7298838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1997,7 +2003,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2009,17 +2014,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088870</v>
+        <v>120088849</v>
       </c>
       <c r="B15" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777507</v>
+        <v>777511</v>
       </c>
       <c r="R15" t="n">
-        <v>7299148</v>
+        <v>7298804</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088831</v>
+        <v>120088854</v>
       </c>
       <c r="B16" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777532</v>
+        <v>777398</v>
       </c>
       <c r="R16" t="n">
-        <v>7299086</v>
+        <v>7298832</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088845</v>
+        <v>120088851</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777508</v>
+        <v>777457</v>
       </c>
       <c r="R17" t="n">
-        <v>7298912</v>
+        <v>7298804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088843</v>
+        <v>120088864</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2334,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777504</v>
+        <v>777355</v>
       </c>
       <c r="R18" t="n">
-        <v>7298945</v>
+        <v>7298843</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088852</v>
+        <v>120088828</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2436,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777427</v>
+        <v>777455</v>
       </c>
       <c r="R19" t="n">
-        <v>7298810</v>
+        <v>7298795</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,7 +2531,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088865</v>
+        <v>120088850</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2560,20 +2565,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777415</v>
+        <v>777502</v>
       </c>
       <c r="R20" t="n">
-        <v>7298849</v>
+        <v>7298806</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,7 +2615,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,17 +2626,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088864</v>
+        <v>120088852</v>
       </c>
       <c r="B21" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2645,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777355</v>
+        <v>777427</v>
       </c>
       <c r="R21" t="n">
-        <v>7298843</v>
+        <v>7298810</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,10 +2735,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088828</v>
+        <v>120088865</v>
       </c>
       <c r="B22" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,38 +2747,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777455</v>
+        <v>777415</v>
       </c>
       <c r="R22" t="n">
-        <v>7298795</v>
+        <v>7298849</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,6 +2823,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2830,17 +2835,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088834</v>
+        <v>120088841</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777529</v>
+        <v>777505</v>
       </c>
       <c r="R23" t="n">
-        <v>7299081</v>
+        <v>7299152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088862</v>
+        <v>120088870</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2951,25 +2956,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777412</v>
+        <v>777507</v>
       </c>
       <c r="R24" t="n">
-        <v>7298815</v>
+        <v>7299148</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3041,7 +3046,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088841</v>
+        <v>120088846</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3081,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777505</v>
+        <v>777509</v>
       </c>
       <c r="R25" t="n">
-        <v>7299152</v>
+        <v>7298862</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3148,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088855</v>
+        <v>120088840</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3183,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777392</v>
+        <v>777485</v>
       </c>
       <c r="R26" t="n">
-        <v>7298835</v>
+        <v>7299147</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3245,7 +3250,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088858</v>
+        <v>120088843</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3285,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777356</v>
+        <v>777504</v>
       </c>
       <c r="R27" t="n">
-        <v>7298837</v>
+        <v>7298945</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,37 +3352,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088868</v>
+        <v>120088862</v>
       </c>
       <c r="B28" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777492</v>
+        <v>777412</v>
       </c>
       <c r="R28" t="n">
-        <v>7299157</v>
+        <v>7298815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,7 +3454,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088867</v>
+        <v>120088853</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3483,20 +3488,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777364</v>
+        <v>777429</v>
       </c>
       <c r="R29" t="n">
-        <v>7298811</v>
+        <v>7298824</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,7 +3538,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3549,14 +3549,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088842</v>
+        <v>120088857</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777507</v>
+        <v>777367</v>
       </c>
       <c r="R30" t="n">
-        <v>7299126</v>
+        <v>7298814</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3760,10 +3760,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088827</v>
+        <v>120088863</v>
       </c>
       <c r="B32" t="n">
-        <v>87423</v>
+        <v>82321</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3776,21 +3776,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777473</v>
+        <v>777515</v>
       </c>
       <c r="R32" t="n">
-        <v>7298817</v>
+        <v>7299124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088857</v>
+        <v>120088834</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777367</v>
+        <v>777529</v>
       </c>
       <c r="R33" t="n">
-        <v>7298814</v>
+        <v>7299081</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109444</v>
+        <v>120109447</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777573</v>
+        <v>777398</v>
       </c>
       <c r="R34" t="n">
-        <v>7299187</v>
+        <v>7298959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109452</v>
+        <v>120109445</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777449</v>
+        <v>777555</v>
       </c>
       <c r="R35" t="n">
-        <v>7298879</v>
+        <v>7299109</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109445</v>
+        <v>120109450</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777555</v>
+        <v>777403</v>
       </c>
       <c r="R37" t="n">
-        <v>7299109</v>
+        <v>7298895</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109457</v>
+        <v>120109453</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777600</v>
+        <v>777456</v>
       </c>
       <c r="R38" t="n">
-        <v>7299114</v>
+        <v>7298884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109449</v>
+        <v>120109452</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777456</v>
+        <v>777449</v>
       </c>
       <c r="R39" t="n">
-        <v>7298953</v>
+        <v>7298879</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109455</v>
+        <v>120109465</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4588,25 +4588,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777511</v>
+        <v>777595</v>
       </c>
       <c r="R40" t="n">
-        <v>7298851</v>
+        <v>7299138</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4780,10 +4780,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109465</v>
+        <v>120109454</v>
       </c>
       <c r="B42" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4792,25 +4792,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777595</v>
+        <v>777458</v>
       </c>
       <c r="R42" t="n">
-        <v>7299138</v>
+        <v>7298865</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109454</v>
+        <v>120109459</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777458</v>
+        <v>777599</v>
       </c>
       <c r="R43" t="n">
-        <v>7298865</v>
+        <v>7299147</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109459</v>
+        <v>120109449</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777599</v>
+        <v>777456</v>
       </c>
       <c r="R44" t="n">
-        <v>7299147</v>
+        <v>7298953</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109443</v>
+        <v>120109455</v>
       </c>
       <c r="B45" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5098,25 +5098,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777444</v>
+        <v>777511</v>
       </c>
       <c r="R45" t="n">
-        <v>7298925</v>
+        <v>7298851</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109450</v>
+        <v>120109457</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777403</v>
+        <v>777600</v>
       </c>
       <c r="R46" t="n">
-        <v>7298895</v>
+        <v>7299114</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109447</v>
+        <v>120109444</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777398</v>
+        <v>777573</v>
       </c>
       <c r="R47" t="n">
-        <v>7298959</v>
+        <v>7299187</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109453</v>
+        <v>120109443</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5404,25 +5404,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777456</v>
+        <v>777444</v>
       </c>
       <c r="R48" t="n">
-        <v>7298884</v>
+        <v>7298925</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088866</v>
+        <v>120088853</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -821,20 +821,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777389</v>
+        <v>777429</v>
       </c>
       <c r="R3" t="n">
-        <v>7298847</v>
+        <v>7298824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,14 +882,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088855</v>
+        <v>120088841</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777392</v>
+        <v>777505</v>
       </c>
       <c r="R4" t="n">
-        <v>7298835</v>
+        <v>7299152</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088842</v>
+        <v>120088850</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777507</v>
+        <v>777502</v>
       </c>
       <c r="R5" t="n">
-        <v>7299126</v>
+        <v>7298806</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,37 +1093,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088868</v>
+        <v>120088827</v>
       </c>
       <c r="B6" t="n">
-        <v>95225</v>
+        <v>87423</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777492</v>
+        <v>777473</v>
       </c>
       <c r="R6" t="n">
-        <v>7299157</v>
+        <v>7298817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088867</v>
+        <v>120088858</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1234,20 +1229,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777364</v>
+        <v>777356</v>
       </c>
       <c r="R7" t="n">
-        <v>7298811</v>
+        <v>7298837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1279,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1300,17 +1290,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088869</v>
+        <v>120088846</v>
       </c>
       <c r="B8" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777505</v>
+        <v>777509</v>
       </c>
       <c r="R8" t="n">
-        <v>7299155</v>
+        <v>7298862</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088845</v>
+        <v>120088828</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777508</v>
+        <v>777455</v>
       </c>
       <c r="R9" t="n">
-        <v>7298912</v>
+        <v>7298795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088847</v>
+        <v>120088831</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777517</v>
+        <v>777532</v>
       </c>
       <c r="R10" t="n">
-        <v>7298828</v>
+        <v>7299086</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088858</v>
+        <v>120088870</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777356</v>
+        <v>777507</v>
       </c>
       <c r="R11" t="n">
-        <v>7298837</v>
+        <v>7299148</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,14 +1705,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088831</v>
+        <v>120088868</v>
       </c>
       <c r="B12" t="n">
-        <v>79652</v>
+        <v>95225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1731,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777532</v>
+        <v>777492</v>
       </c>
       <c r="R12" t="n">
-        <v>7299086</v>
+        <v>7299157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088827</v>
+        <v>120088840</v>
       </c>
       <c r="B13" t="n">
-        <v>87423</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777473</v>
+        <v>777485</v>
       </c>
       <c r="R13" t="n">
-        <v>7298817</v>
+        <v>7299147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088829</v>
+        <v>120088847</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777417</v>
+        <v>777517</v>
       </c>
       <c r="R14" t="n">
-        <v>7298838</v>
+        <v>7298828</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088849</v>
+        <v>120088843</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2061,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777511</v>
+        <v>777504</v>
       </c>
       <c r="R15" t="n">
-        <v>7298804</v>
+        <v>7298945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2113,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088854</v>
+        <v>120088856</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2163,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777398</v>
+        <v>777378</v>
       </c>
       <c r="R16" t="n">
-        <v>7298832</v>
+        <v>7298811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088851</v>
+        <v>120088869</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777457</v>
+        <v>777505</v>
       </c>
       <c r="R17" t="n">
-        <v>7298804</v>
+        <v>7299155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088828</v>
+        <v>120088863</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>82321</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,21 +2435,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777455</v>
+        <v>777515</v>
       </c>
       <c r="R19" t="n">
-        <v>7298795</v>
+        <v>7299124</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,7 +2521,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088850</v>
+        <v>120088852</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777502</v>
+        <v>777427</v>
       </c>
       <c r="R20" t="n">
-        <v>7298806</v>
+        <v>7298810</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088852</v>
+        <v>120088834</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2645,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777427</v>
+        <v>777529</v>
       </c>
       <c r="R21" t="n">
-        <v>7298810</v>
+        <v>7299081</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,7 +2725,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088865</v>
+        <v>120088857</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -2769,20 +2759,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777415</v>
+        <v>777367</v>
       </c>
       <c r="R22" t="n">
-        <v>7298849</v>
+        <v>7298814</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,7 +2809,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2835,17 +2820,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088841</v>
+        <v>120088829</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>90545</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,25 +2839,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777505</v>
+        <v>777417</v>
       </c>
       <c r="R23" t="n">
-        <v>7299152</v>
+        <v>7298838</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2944,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088870</v>
+        <v>120088851</v>
       </c>
       <c r="B24" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2956,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777507</v>
+        <v>777457</v>
       </c>
       <c r="R24" t="n">
-        <v>7299148</v>
+        <v>7298804</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088846</v>
+        <v>120088862</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3058,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3086,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777509</v>
+        <v>777412</v>
       </c>
       <c r="R25" t="n">
-        <v>7298862</v>
+        <v>7298815</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088840</v>
+        <v>120088854</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3188,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777485</v>
+        <v>777398</v>
       </c>
       <c r="R26" t="n">
-        <v>7299147</v>
+        <v>7298832</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088843</v>
+        <v>120088855</v>
       </c>
       <c r="B27" t="n">
         <v>97930</v>
@@ -3290,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777504</v>
+        <v>777392</v>
       </c>
       <c r="R27" t="n">
-        <v>7298945</v>
+        <v>7298835</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088862</v>
+        <v>120088866</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,38 +3349,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777412</v>
+        <v>777389</v>
       </c>
       <c r="R28" t="n">
-        <v>7298815</v>
+        <v>7298847</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3436,6 +3425,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3447,14 +3437,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088853</v>
+        <v>120088849</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3494,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777429</v>
+        <v>777511</v>
       </c>
       <c r="R29" t="n">
-        <v>7298824</v>
+        <v>7298804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3546,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088857</v>
+        <v>120088867</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3590,16 +3580,20 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777367</v>
+        <v>777364</v>
       </c>
       <c r="R30" t="n">
-        <v>7298814</v>
+        <v>7298811</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3640,6 +3634,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3651,14 +3646,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088856</v>
+        <v>120088842</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -3698,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777378</v>
+        <v>777507</v>
       </c>
       <c r="R31" t="n">
-        <v>7298811</v>
+        <v>7299126</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088863</v>
+        <v>120088845</v>
       </c>
       <c r="B32" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3772,25 +3767,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3800,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777515</v>
+        <v>777508</v>
       </c>
       <c r="R32" t="n">
-        <v>7299124</v>
+        <v>7298912</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088834</v>
+        <v>120088865</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3874,38 +3869,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777529</v>
+        <v>777415</v>
       </c>
       <c r="R33" t="n">
-        <v>7299081</v>
+        <v>7298849</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3946,6 +3945,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3957,14 +3957,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109447</v>
+        <v>120109453</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4004,10 +4004,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777398</v>
+        <v>777456</v>
       </c>
       <c r="R34" t="n">
-        <v>7298959</v>
+        <v>7298884</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109445</v>
+        <v>120109454</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777555</v>
+        <v>777458</v>
       </c>
       <c r="R35" t="n">
-        <v>7299109</v>
+        <v>7298865</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109448</v>
+        <v>120109459</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777417</v>
+        <v>777599</v>
       </c>
       <c r="R36" t="n">
-        <v>7298952</v>
+        <v>7299147</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109450</v>
+        <v>120109457</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777403</v>
+        <v>777600</v>
       </c>
       <c r="R37" t="n">
-        <v>7298895</v>
+        <v>7299114</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109453</v>
+        <v>120109452</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777456</v>
+        <v>777449</v>
       </c>
       <c r="R38" t="n">
-        <v>7298884</v>
+        <v>7298879</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109452</v>
+        <v>120109446</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777449</v>
+        <v>777434</v>
       </c>
       <c r="R39" t="n">
-        <v>7298879</v>
+        <v>7298954</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4576,10 +4576,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109465</v>
+        <v>120109449</v>
       </c>
       <c r="B40" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4588,25 +4588,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777595</v>
+        <v>777456</v>
       </c>
       <c r="R40" t="n">
-        <v>7299138</v>
+        <v>7298953</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109446</v>
+        <v>120109465</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4690,25 +4690,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777434</v>
+        <v>777595</v>
       </c>
       <c r="R41" t="n">
-        <v>7298954</v>
+        <v>7299138</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109454</v>
+        <v>120109455</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777458</v>
+        <v>777511</v>
       </c>
       <c r="R42" t="n">
-        <v>7298865</v>
+        <v>7298851</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109459</v>
+        <v>120109451</v>
       </c>
       <c r="B43" t="n">
         <v>97930</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777599</v>
+        <v>777444</v>
       </c>
       <c r="R43" t="n">
-        <v>7299147</v>
+        <v>7298882</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4984,7 +4984,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109449</v>
+        <v>120109447</v>
       </c>
       <c r="B44" t="n">
         <v>97930</v>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777456</v>
+        <v>777398</v>
       </c>
       <c r="R44" t="n">
-        <v>7298953</v>
+        <v>7298959</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109455</v>
+        <v>120109450</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5126,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777511</v>
+        <v>777403</v>
       </c>
       <c r="R45" t="n">
-        <v>7298851</v>
+        <v>7298895</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,7 +5188,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109457</v>
+        <v>120109445</v>
       </c>
       <c r="B46" t="n">
         <v>97930</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777600</v>
+        <v>777555</v>
       </c>
       <c r="R46" t="n">
-        <v>7299114</v>
+        <v>7299109</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109444</v>
+        <v>120109448</v>
       </c>
       <c r="B47" t="n">
         <v>97930</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777573</v>
+        <v>777417</v>
       </c>
       <c r="R47" t="n">
-        <v>7299187</v>
+        <v>7298952</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109443</v>
+        <v>120109444</v>
       </c>
       <c r="B48" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5404,25 +5404,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777444</v>
+        <v>777573</v>
       </c>
       <c r="R48" t="n">
-        <v>7298925</v>
+        <v>7299187</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109451</v>
+        <v>120109443</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5506,25 +5506,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
         <v>777444</v>
       </c>
       <c r="R49" t="n">
-        <v>7298882</v>
+        <v>7298925</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088828</v>
+        <v>120088870</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>95225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777455</v>
+        <v>777507</v>
       </c>
       <c r="R9" t="n">
-        <v>7298795</v>
+        <v>7299148</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,14 +1501,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088831</v>
+        <v>120088868</v>
       </c>
       <c r="B10" t="n">
-        <v>79652</v>
+        <v>95225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777532</v>
+        <v>777492</v>
       </c>
       <c r="R10" t="n">
-        <v>7299086</v>
+        <v>7299157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088870</v>
+        <v>120088828</v>
       </c>
       <c r="B11" t="n">
-        <v>95225</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777507</v>
+        <v>777455</v>
       </c>
       <c r="R11" t="n">
-        <v>7299148</v>
+        <v>7298795</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,14 +1705,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088868</v>
+        <v>120088831</v>
       </c>
       <c r="B12" t="n">
-        <v>95225</v>
+        <v>79652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777492</v>
+        <v>777532</v>
       </c>
       <c r="R12" t="n">
-        <v>7299157</v>
+        <v>7299086</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088849</v>
+        <v>120088867</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3478,16 +3478,20 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777511</v>
+        <v>777364</v>
       </c>
       <c r="R29" t="n">
-        <v>7298804</v>
+        <v>7298811</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,6 +3532,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3539,14 +3544,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088867</v>
+        <v>120088849</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3580,20 +3585,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777364</v>
+        <v>777511</v>
       </c>
       <c r="R30" t="n">
-        <v>7298811</v>
+        <v>7298804</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,7 +3635,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -5392,10 +5392,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109444</v>
+        <v>120109443</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>96891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5404,25 +5404,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777573</v>
+        <v>777444</v>
       </c>
       <c r="R48" t="n">
-        <v>7299187</v>
+        <v>7298925</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109443</v>
+        <v>120109444</v>
       </c>
       <c r="B49" t="n">
-        <v>96891</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5506,25 +5506,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777444</v>
+        <v>777573</v>
       </c>
       <c r="R49" t="n">
-        <v>7298925</v>
+        <v>7299187</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5594,6 +5594,1277 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128404388</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>777495</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7298785</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128404395</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>777614</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7299189</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128404405</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80170</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>777590</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7299136</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128404390</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>777504</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7298820</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128404384</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>777536</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7299152</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128404385</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>777549</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7299126</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128404377</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97353</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>777595</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7299107</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128404402</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>777608</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7299215</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128404389</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>777484</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7298784</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128404394</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>777610</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7299180</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128404392</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>777498</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7298870</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128404386</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>777534</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7298905</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128404381</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>777481</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7298773</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97353</v>
+        <v>97355</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92841</v>
+        <v>92843</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>128404405</v>
       </c>
       <c r="B52" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5790,32 +5790,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128404405</v>
+        <v>128404390</v>
       </c>
       <c r="B52" t="n">
-        <v>80223</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777590</v>
+        <v>777504</v>
       </c>
       <c r="R52" t="n">
-        <v>7299136</v>
+        <v>7298820</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5861,6 +5861,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5887,32 +5892,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128404390</v>
+        <v>128404405</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>80223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5922,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777504</v>
+        <v>777590</v>
       </c>
       <c r="R53" t="n">
-        <v>7298820</v>
+        <v>7299136</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5958,11 +5963,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5790,32 +5790,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128404390</v>
+        <v>128404405</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>80227</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777504</v>
+        <v>777590</v>
       </c>
       <c r="R52" t="n">
-        <v>7298820</v>
+        <v>7299136</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5861,11 +5861,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5892,32 +5887,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128404405</v>
+        <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>80223</v>
+        <v>98585</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777590</v>
+        <v>777504</v>
       </c>
       <c r="R53" t="n">
-        <v>7299136</v>
+        <v>7298820</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5963,6 +5958,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5790,32 +5790,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128404405</v>
+        <v>128404390</v>
       </c>
       <c r="B52" t="n">
-        <v>80227</v>
+        <v>98585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777590</v>
+        <v>777504</v>
       </c>
       <c r="R52" t="n">
-        <v>7299136</v>
+        <v>7298820</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5861,6 +5861,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5887,32 +5892,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128404390</v>
+        <v>128404405</v>
       </c>
       <c r="B53" t="n">
-        <v>98585</v>
+        <v>80227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5922,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777504</v>
+        <v>777590</v>
       </c>
       <c r="R53" t="n">
-        <v>7298820</v>
+        <v>7299136</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5958,11 +5963,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5790,32 +5790,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128404390</v>
+        <v>128404405</v>
       </c>
       <c r="B52" t="n">
-        <v>98585</v>
+        <v>80229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777504</v>
+        <v>777590</v>
       </c>
       <c r="R52" t="n">
-        <v>7298820</v>
+        <v>7299136</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5861,11 +5861,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5892,32 +5887,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128404405</v>
+        <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>80227</v>
+        <v>98588</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777590</v>
+        <v>777504</v>
       </c>
       <c r="R53" t="n">
-        <v>7299136</v>
+        <v>7298820</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5963,6 +5958,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>128404405</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92950</v>
+        <v>92977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>128404405</v>
       </c>
       <c r="B52" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92977</v>
+        <v>92989</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>128404405</v>
       </c>
       <c r="B52" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>128404392</v>
       </c>
       <c r="B60" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>128404386</v>
       </c>
       <c r="B61" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5790,32 +5790,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128404405</v>
+        <v>128404390</v>
       </c>
       <c r="B52" t="n">
-        <v>80264</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777590</v>
+        <v>777504</v>
       </c>
       <c r="R52" t="n">
-        <v>7299136</v>
+        <v>7298820</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5861,6 +5861,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5887,32 +5892,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128404390</v>
+        <v>128404405</v>
       </c>
       <c r="B53" t="n">
-        <v>98636</v>
+        <v>80264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5922,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777504</v>
+        <v>777590</v>
       </c>
       <c r="R53" t="n">
-        <v>7298820</v>
+        <v>7299136</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5958,11 +5963,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -5599,7 +5599,7 @@
         <v>128404388</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128404395</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5790,32 +5790,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128404390</v>
+        <v>128404405</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>80169</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777504</v>
+        <v>777590</v>
       </c>
       <c r="R52" t="n">
-        <v>7298820</v>
+        <v>7299136</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5861,11 +5861,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5892,32 +5887,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128404405</v>
+        <v>128404390</v>
       </c>
       <c r="B53" t="n">
-        <v>80264</v>
+        <v>98643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5927,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777590</v>
+        <v>777504</v>
       </c>
       <c r="R53" t="n">
-        <v>7299136</v>
+        <v>7298820</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5963,6 +5958,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5992,7 +5992,7 @@
         <v>128404384</v>
       </c>
       <c r="B54" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>128404385</v>
       </c>
       <c r="B55" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>128404377</v>
       </c>
       <c r="B56" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>128404402</v>
       </c>
       <c r="B57" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>128404389</v>
       </c>
       <c r="B58" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         <v>128404394</v>
       </c>
       <c r="B59" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128404392</v>
+        <v>128404386</v>
       </c>
       <c r="B60" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6611,10 +6611,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>777498</v>
+        <v>777534</v>
       </c>
       <c r="R60" t="n">
-        <v>7298870</v>
+        <v>7298905</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6673,10 +6673,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128404386</v>
+        <v>128404392</v>
       </c>
       <c r="B61" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>777534</v>
+        <v>777498</v>
       </c>
       <c r="R61" t="n">
-        <v>7298905</v>
+        <v>7298870</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6773,7 +6773,7 @@
         <v>128404381</v>
       </c>
       <c r="B62" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6865,6 +6865,108 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129299334</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>777555</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7299104</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Mattbildande,riklig förekomst 1×2 m</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -6870,7 +6870,7 @@
         <v>129299334</v>
       </c>
       <c r="B63" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>62186960</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>777466.8922016784</v>
+        <v>777467</v>
       </c>
       <c r="R2" t="n">
-        <v>7298800.909519275</v>
+        <v>7298801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-08-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120088865</v>
+        <v>120088860</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>777415</v>
+        <v>777547</v>
       </c>
       <c r="R3" t="n">
-        <v>7298849</v>
+        <v>7299037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,44 +862,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120088870</v>
+        <v>120088863</v>
       </c>
       <c r="B4" t="n">
-        <v>95225</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>777507</v>
+        <v>777515</v>
       </c>
       <c r="R4" t="n">
-        <v>7299148</v>
+        <v>7299124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120088834</v>
+        <v>120088864</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>777529</v>
+        <v>777355</v>
       </c>
       <c r="R5" t="n">
-        <v>7299081</v>
+        <v>7298843</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120088852</v>
+        <v>120109465</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>777427</v>
+        <v>777595</v>
       </c>
       <c r="R6" t="n">
-        <v>7298810</v>
+        <v>7299138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120088828</v>
+        <v>128404381</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>777455</v>
+        <v>777481</v>
       </c>
       <c r="R7" t="n">
-        <v>7298795</v>
+        <v>7298773</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120088853</v>
+        <v>120088868</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>777429</v>
+        <v>777492</v>
       </c>
       <c r="R8" t="n">
-        <v>7298824</v>
+        <v>7299157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120088855</v>
+        <v>120088869</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>777392</v>
+        <v>777505</v>
       </c>
       <c r="R9" t="n">
-        <v>7298835</v>
+        <v>7299155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120088845</v>
+        <v>120088870</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>777508</v>
+        <v>777507</v>
       </c>
       <c r="R10" t="n">
-        <v>7298912</v>
+        <v>7299148</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120088827</v>
+        <v>120088871</v>
       </c>
       <c r="B11" t="n">
-        <v>87423</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4412</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>777473</v>
+        <v>777334</v>
       </c>
       <c r="R11" t="n">
-        <v>7298817</v>
+        <v>7298827</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120088829</v>
+        <v>120088827</v>
       </c>
       <c r="B12" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>777417</v>
+        <v>777473</v>
       </c>
       <c r="R12" t="n">
-        <v>7298838</v>
+        <v>7298817</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120088842</v>
+        <v>120088829</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>777507</v>
+        <v>777417</v>
       </c>
       <c r="R13" t="n">
-        <v>7299126</v>
+        <v>7298838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088869</v>
+        <v>120088862</v>
       </c>
       <c r="B14" t="n">
-        <v>95225</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777505</v>
+        <v>777412</v>
       </c>
       <c r="R14" t="n">
-        <v>7299155</v>
+        <v>7298815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088849</v>
+        <v>120088828</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777511</v>
+        <v>777455</v>
       </c>
       <c r="R15" t="n">
-        <v>7298804</v>
+        <v>7298795</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088846</v>
+        <v>120088834</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777509</v>
+        <v>777529</v>
       </c>
       <c r="R16" t="n">
-        <v>7298862</v>
+        <v>7299081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,54 +2130,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088867</v>
+        <v>120088835</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777364</v>
+        <v>777330</v>
       </c>
       <c r="R17" t="n">
-        <v>7298811</v>
+        <v>7298837</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,7 +2209,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,44 +2220,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120088840</v>
+        <v>129299329</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2262,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777485</v>
+        <v>777663</v>
       </c>
       <c r="R18" t="n">
-        <v>7299147</v>
+        <v>7299175</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2397,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088856</v>
+        <v>120088831</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777378</v>
+        <v>777532</v>
       </c>
       <c r="R19" t="n">
-        <v>7298811</v>
+        <v>7299086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120088864</v>
+        <v>129299328</v>
       </c>
       <c r="B20" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,13 +2456,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777355</v>
+        <v>777658</v>
       </c>
       <c r="R20" t="n">
-        <v>7298843</v>
+        <v>7299175</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2601,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2633,32 +2518,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120088862</v>
+        <v>128404405</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2673,13 +2553,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777412</v>
+        <v>777590</v>
       </c>
       <c r="R21" t="n">
-        <v>7298815</v>
+        <v>7299136</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2703,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120088857</v>
+        <v>129299339</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777367</v>
+        <v>777648</v>
       </c>
       <c r="R22" t="n">
-        <v>7298814</v>
+        <v>7299164</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2805,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,54 +2712,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088866</v>
+        <v>120088836</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777389</v>
+        <v>777534</v>
       </c>
       <c r="R23" t="n">
-        <v>7298847</v>
+        <v>7298748</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,7 +2791,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2937,44 +2802,39 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088831</v>
+        <v>120088840</v>
       </c>
       <c r="B24" t="n">
-        <v>79652</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2984,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777532</v>
+        <v>777485</v>
       </c>
       <c r="R24" t="n">
-        <v>7299086</v>
+        <v>7299147</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3046,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088847</v>
+        <v>120088841</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3086,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777517</v>
+        <v>777505</v>
       </c>
       <c r="R25" t="n">
-        <v>7298828</v>
+        <v>7299152</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088850</v>
+        <v>120088842</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777502</v>
+        <v>777507</v>
       </c>
       <c r="R26" t="n">
-        <v>7298806</v>
+        <v>7299126</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,37 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088863</v>
+        <v>120088843</v>
       </c>
       <c r="B27" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777515</v>
+        <v>777504</v>
       </c>
       <c r="R27" t="n">
-        <v>7299124</v>
+        <v>7298945</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3352,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088841</v>
+        <v>120088845</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3392,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777505</v>
+        <v>777508</v>
       </c>
       <c r="R28" t="n">
-        <v>7299152</v>
+        <v>7298912</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088858</v>
+        <v>120088846</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777356</v>
+        <v>777509</v>
       </c>
       <c r="R29" t="n">
-        <v>7298837</v>
+        <v>7298862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088851</v>
+        <v>120088847</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3596,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777457</v>
+        <v>777517</v>
       </c>
       <c r="R30" t="n">
-        <v>7298804</v>
+        <v>7298828</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3658,37 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088868</v>
+        <v>120088849</v>
       </c>
       <c r="B31" t="n">
-        <v>95225</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3698,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777492</v>
+        <v>777511</v>
       </c>
       <c r="R31" t="n">
-        <v>7299157</v>
+        <v>7298804</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3760,15 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088843</v>
+        <v>120088850</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3800,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777504</v>
+        <v>777502</v>
       </c>
       <c r="R32" t="n">
-        <v>7298945</v>
+        <v>7298806</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088854</v>
+        <v>120088851</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3902,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777398</v>
+        <v>777457</v>
       </c>
       <c r="R33" t="n">
-        <v>7298832</v>
+        <v>7298804</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,15 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120109453</v>
+        <v>120088852</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4004,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777456</v>
+        <v>777427</v>
       </c>
       <c r="R34" t="n">
-        <v>7298884</v>
+        <v>7298810</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4034,12 +3844,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4054,27 +3864,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120109457</v>
+        <v>120088853</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777600</v>
+        <v>777429</v>
       </c>
       <c r="R35" t="n">
-        <v>7299114</v>
+        <v>7298824</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4136,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4156,27 +3961,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120109452</v>
+        <v>120088854</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4208,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777449</v>
+        <v>777398</v>
       </c>
       <c r="R36" t="n">
-        <v>7298879</v>
+        <v>7298832</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4238,12 +4038,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4258,27 +4058,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120109447</v>
+        <v>120088855</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4310,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777398</v>
+        <v>777392</v>
       </c>
       <c r="R37" t="n">
-        <v>7298959</v>
+        <v>7298835</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4340,12 +4135,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4360,27 +4155,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120109450</v>
+        <v>120088856</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4412,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777403</v>
+        <v>777378</v>
       </c>
       <c r="R38" t="n">
-        <v>7298895</v>
+        <v>7298811</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4442,12 +4232,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4462,27 +4252,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120109459</v>
+        <v>120088857</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4514,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777599</v>
+        <v>777367</v>
       </c>
       <c r="R39" t="n">
-        <v>7299147</v>
+        <v>7298814</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,12 +4329,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4564,49 +4349,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120109465</v>
+        <v>120088858</v>
       </c>
       <c r="B40" t="n">
-        <v>82321</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4616,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777595</v>
+        <v>777356</v>
       </c>
       <c r="R40" t="n">
-        <v>7299138</v>
+        <v>7298837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,12 +4426,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4666,27 +4446,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120109455</v>
+        <v>120088865</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4712,16 +4487,20 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777511</v>
+        <v>777415</v>
       </c>
       <c r="R41" t="n">
-        <v>7298851</v>
+        <v>7298849</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,12 +4527,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4762,33 +4541,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120109454</v>
+        <v>120088866</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4814,16 +4589,20 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777458</v>
+        <v>777389</v>
       </c>
       <c r="R42" t="n">
-        <v>7298865</v>
+        <v>7298847</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,12 +4629,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4864,33 +4643,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120109446</v>
+        <v>120088867</v>
       </c>
       <c r="B43" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,16 +4691,20 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777434</v>
+        <v>777364</v>
       </c>
       <c r="R43" t="n">
-        <v>7298954</v>
+        <v>7298811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4952,12 +4731,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4966,33 +4745,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109445</v>
+        <v>120109444</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5024,10 +4799,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777555</v>
+        <v>777573</v>
       </c>
       <c r="R44" t="n">
-        <v>7299109</v>
+        <v>7299187</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,15 +4861,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109448</v>
+        <v>120109445</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5126,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777417</v>
+        <v>777555</v>
       </c>
       <c r="R45" t="n">
-        <v>7298952</v>
+        <v>7299109</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,15 +4958,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109451</v>
+        <v>120109446</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5228,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777444</v>
+        <v>777434</v>
       </c>
       <c r="R46" t="n">
-        <v>7298882</v>
+        <v>7298954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,15 +5055,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109449</v>
+        <v>120109447</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5330,10 +5090,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777456</v>
+        <v>777398</v>
       </c>
       <c r="R47" t="n">
-        <v>7298953</v>
+        <v>7298959</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5392,15 +5152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109444</v>
+        <v>120109448</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5432,10 +5187,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777573</v>
+        <v>777417</v>
       </c>
       <c r="R48" t="n">
-        <v>7299187</v>
+        <v>7298952</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5494,37 +5249,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109443</v>
+        <v>120109449</v>
       </c>
       <c r="B49" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5534,10 +5284,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777444</v>
+        <v>777456</v>
       </c>
       <c r="R49" t="n">
-        <v>7298925</v>
+        <v>7298953</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5596,10 +5346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128404388</v>
+        <v>120109450</v>
       </c>
       <c r="B50" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5631,13 +5381,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>777495</v>
+        <v>777403</v>
       </c>
       <c r="R50" t="n">
-        <v>7298785</v>
+        <v>7298895</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5661,12 +5411,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5681,22 +5431,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128404395</v>
+        <v>120109451</v>
       </c>
       <c r="B51" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5728,13 +5478,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>777614</v>
+        <v>777444</v>
       </c>
       <c r="R51" t="n">
-        <v>7299189</v>
+        <v>7298882</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5758,12 +5508,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5778,44 +5528,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128404405</v>
+        <v>120109452</v>
       </c>
       <c r="B52" t="n">
-        <v>80169</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5825,13 +5575,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777590</v>
+        <v>777449</v>
       </c>
       <c r="R52" t="n">
-        <v>7299136</v>
+        <v>7298879</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5855,12 +5605,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5875,22 +5625,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128404390</v>
+        <v>120109453</v>
       </c>
       <c r="B53" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5922,13 +5672,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777504</v>
+        <v>777456</v>
       </c>
       <c r="R53" t="n">
-        <v>7298820</v>
+        <v>7298884</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5952,17 +5702,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5977,22 +5722,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128404384</v>
+        <v>120109454</v>
       </c>
       <c r="B54" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,13 +5769,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>777536</v>
+        <v>777458</v>
       </c>
       <c r="R54" t="n">
-        <v>7299152</v>
+        <v>7298865</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6054,12 +5799,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6074,22 +5819,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128404385</v>
+        <v>120109455</v>
       </c>
       <c r="B55" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6121,13 +5866,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>777549</v>
+        <v>777511</v>
       </c>
       <c r="R55" t="n">
-        <v>7299126</v>
+        <v>7298851</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6151,12 +5896,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6171,44 +5916,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128404377</v>
+        <v>120109456</v>
       </c>
       <c r="B56" t="n">
-        <v>97516</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6218,13 +5963,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>777595</v>
+        <v>777582</v>
       </c>
       <c r="R56" t="n">
-        <v>7299107</v>
+        <v>7299080</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6248,12 +5993,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6268,22 +6013,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128404402</v>
+        <v>120109457</v>
       </c>
       <c r="B57" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,13 +6060,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>777608</v>
+        <v>777600</v>
       </c>
       <c r="R57" t="n">
-        <v>7299215</v>
+        <v>7299114</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6345,12 +6090,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6365,22 +6110,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128404389</v>
+        <v>120109459</v>
       </c>
       <c r="B58" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6412,13 +6157,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>777484</v>
+        <v>777599</v>
       </c>
       <c r="R58" t="n">
-        <v>7298784</v>
+        <v>7299147</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6442,12 +6187,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6462,22 +6207,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128404394</v>
+        <v>120109460</v>
       </c>
       <c r="B59" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6509,13 +6254,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>777610</v>
+        <v>777629</v>
       </c>
       <c r="R59" t="n">
-        <v>7299180</v>
+        <v>7299201</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6539,17 +6284,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6564,22 +6304,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128404392</v>
+        <v>120109462</v>
       </c>
       <c r="B60" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6611,13 +6351,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>777498</v>
+        <v>777628</v>
       </c>
       <c r="R60" t="n">
-        <v>7298870</v>
+        <v>7299215</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6641,12 +6381,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6661,22 +6401,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128404386</v>
+        <v>128404384</v>
       </c>
       <c r="B61" t="n">
-        <v>98645</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6708,10 +6448,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>777534</v>
+        <v>777536</v>
       </c>
       <c r="R61" t="n">
-        <v>7298905</v>
+        <v>7299152</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6770,32 +6510,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128404381</v>
+        <v>128404385</v>
       </c>
       <c r="B62" t="n">
-        <v>93000</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6805,10 +6545,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>777481</v>
+        <v>777549</v>
       </c>
       <c r="R62" t="n">
-        <v>7298773</v>
+        <v>7299126</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6867,10 +6607,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129299334</v>
+        <v>128404386</v>
       </c>
       <c r="B63" t="n">
-        <v>98769</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6902,10 +6642,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777555</v>
+        <v>777534</v>
       </c>
       <c r="R63" t="n">
-        <v>7299104</v>
+        <v>7298905</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6932,17 +6672,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Mattbildande,riklig förekomst 1×2 m</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6966,6 +6701,1782 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128404388</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>777495</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7298785</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128404389</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>777484</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7298784</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128404390</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>777504</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7298820</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128404392</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>777498</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7298870</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128404393</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>777550</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7298893</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128404394</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>777610</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7299180</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128404395</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>777614</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7299189</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128404398</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>777628</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7299203</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128404399</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>777619</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7299211</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128404402</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>777608</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7299215</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128404403</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>777601</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7299235</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129299331</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>777644</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7299199</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>1×2m</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129299332</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>777646</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7299185</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129299333</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>777663</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7299185</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>4×3m mycket riklig förekomst, mattbildande.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129299334</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>777555</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7299104</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Mattbildande,riklig förekomst 1×2 m</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129299336</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>777522</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7299206</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Förekomst 1m× 2m</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120109443</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>777444</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7298925</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128404377</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>777595</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7299107</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62186960</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088860</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088863</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109465</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088869</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088870</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088871</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088827</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088829</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088862</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088828</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088834</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088835</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299329</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088831</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299328</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404405</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299339</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088836</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088840</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088841</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088842</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088843</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088845</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088846</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088847</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088849</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088850</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088851</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088852</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088853</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088854</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088855</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088856</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088857</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088858</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4557,6 +4757,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088865</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4659,6 +4864,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088866</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4761,6 +4971,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120088867</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4858,6 +5073,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109444</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4955,6 +5175,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109445</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5052,6 +5277,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109446</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5149,6 +5379,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109447</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5246,6 +5481,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109448</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5343,6 +5583,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109449</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5440,6 +5685,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109450</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5537,6 +5787,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109451</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5634,6 +5889,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109452</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5731,6 +5991,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109453</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5828,6 +6093,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109454</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5925,6 +6195,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109455</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6022,6 +6297,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109456</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6119,6 +6399,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109457</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6216,6 +6501,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109459</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6313,6 +6603,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109460</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6410,6 +6705,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109462</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6507,6 +6807,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404384</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6604,6 +6909,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404385</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6701,6 +7011,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404386</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6798,6 +7113,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404388</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6895,6 +7215,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404389</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6997,6 +7322,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404390</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7094,6 +7424,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404392</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7191,6 +7526,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404393</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7293,6 +7633,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404394</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7390,6 +7735,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404395</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7487,6 +7837,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404398</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7584,6 +7939,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404399</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7681,6 +8041,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404402</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7778,6 +8143,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404403</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7880,6 +8250,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299331</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7977,6 +8352,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299332</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8079,6 +8459,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299333</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8181,6 +8566,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299334</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8283,6 +8673,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129299336</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8380,6 +8775,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109443</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8477,8 +8877,95 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128404377</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1904,45 +1904,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120088862</v>
+        <v>120088861</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>85191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5589</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>777412</v>
+        <v>777423</v>
       </c>
       <c r="R14" t="n">
-        <v>7298815</v>
+        <v>7298837</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,6 +1986,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2000,38 +2004,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088862</t>
+          <t>https://artportalen.se/Sighting/120088861</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120088828</v>
+        <v>120088862</v>
       </c>
       <c r="B15" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>777455</v>
+        <v>777412</v>
       </c>
       <c r="R15" t="n">
-        <v>7298795</v>
+        <v>7298815</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,16 +2106,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088828</t>
+          <t>https://artportalen.se/Sighting/120088862</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120088834</v>
+        <v>120088828</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2123,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>777529</v>
+        <v>777455</v>
       </c>
       <c r="R16" t="n">
-        <v>7299081</v>
+        <v>7298795</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,13 +2208,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088834</t>
+          <t>https://artportalen.se/Sighting/120088828</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120088835</v>
+        <v>120088834</v>
       </c>
       <c r="B17" t="n">
         <v>80432</v>
@@ -2245,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>777330</v>
+        <v>777529</v>
       </c>
       <c r="R17" t="n">
-        <v>7298837</v>
+        <v>7299081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,13 +2310,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088835</t>
+          <t>https://artportalen.se/Sighting/120088834</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129299329</v>
+        <v>120088835</v>
       </c>
       <c r="B18" t="n">
         <v>80432</v>
@@ -2347,13 +2351,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>777663</v>
+        <v>777330</v>
       </c>
       <c r="R18" t="n">
-        <v>7299175</v>
+        <v>7298837</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2377,12 +2381,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2408,38 +2412,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299329</t>
+          <t>https://artportalen.se/Sighting/120088835</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120088831</v>
+        <v>129299329</v>
       </c>
       <c r="B19" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,13 +2453,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>777532</v>
+        <v>777663</v>
       </c>
       <c r="R19" t="n">
-        <v>7299086</v>
+        <v>7299175</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2479,12 +2483,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2510,13 +2514,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088831</t>
+          <t>https://artportalen.se/Sighting/129299329</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129299328</v>
+        <v>120088831</v>
       </c>
       <c r="B20" t="n">
         <v>80461</v>
@@ -2551,13 +2555,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>777658</v>
+        <v>777532</v>
       </c>
       <c r="R20" t="n">
-        <v>7299175</v>
+        <v>7299086</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2581,12 +2585,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2612,16 +2616,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299328</t>
+          <t>https://artportalen.se/Sighting/120088831</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128404405</v>
+        <v>129299328</v>
       </c>
       <c r="B21" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,21 +2633,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>777590</v>
+        <v>777658</v>
       </c>
       <c r="R21" t="n">
-        <v>7299136</v>
+        <v>7299175</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2683,12 +2687,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2714,13 +2718,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404405</t>
+          <t>https://artportalen.se/Sighting/129299328</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129299339</v>
+        <v>128404405</v>
       </c>
       <c r="B22" t="n">
         <v>80467</v>
@@ -2755,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>777648</v>
+        <v>777590</v>
       </c>
       <c r="R22" t="n">
-        <v>7299164</v>
+        <v>7299136</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2785,12 +2789,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,38 +2820,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299339</t>
+          <t>https://artportalen.se/Sighting/128404405</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120088836</v>
+        <v>129299339</v>
       </c>
       <c r="B23" t="n">
-        <v>58057</v>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,13 +2861,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>777534</v>
+        <v>777648</v>
       </c>
       <c r="R23" t="n">
-        <v>7298748</v>
+        <v>7299164</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2887,12 +2891,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,38 +2922,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088836</t>
+          <t>https://artportalen.se/Sighting/129299339</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120088840</v>
+        <v>120088836</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>58057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>777485</v>
+        <v>777534</v>
       </c>
       <c r="R24" t="n">
-        <v>7299147</v>
+        <v>7298748</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,13 +3024,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088840</t>
+          <t>https://artportalen.se/Sighting/120088836</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120088841</v>
+        <v>120088840</v>
       </c>
       <c r="B25" t="n">
         <v>99118</v>
@@ -3061,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>777505</v>
+        <v>777485</v>
       </c>
       <c r="R25" t="n">
-        <v>7299152</v>
+        <v>7299147</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,13 +3126,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088841</t>
+          <t>https://artportalen.se/Sighting/120088840</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120088842</v>
+        <v>120088841</v>
       </c>
       <c r="B26" t="n">
         <v>99118</v>
@@ -3163,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>777507</v>
+        <v>777505</v>
       </c>
       <c r="R26" t="n">
-        <v>7299126</v>
+        <v>7299152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,13 +3228,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088842</t>
+          <t>https://artportalen.se/Sighting/120088841</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120088843</v>
+        <v>120088842</v>
       </c>
       <c r="B27" t="n">
         <v>99118</v>
@@ -3265,10 +3269,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>777504</v>
+        <v>777507</v>
       </c>
       <c r="R27" t="n">
-        <v>7298945</v>
+        <v>7299126</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,13 +3330,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088843</t>
+          <t>https://artportalen.se/Sighting/120088842</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120088845</v>
+        <v>120088843</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3367,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>777508</v>
+        <v>777504</v>
       </c>
       <c r="R28" t="n">
-        <v>7298912</v>
+        <v>7298945</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3428,13 +3432,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088845</t>
+          <t>https://artportalen.se/Sighting/120088843</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120088846</v>
+        <v>120088845</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3469,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>777509</v>
+        <v>777508</v>
       </c>
       <c r="R29" t="n">
-        <v>7298862</v>
+        <v>7298912</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3530,13 +3534,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088846</t>
+          <t>https://artportalen.se/Sighting/120088845</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120088847</v>
+        <v>120088846</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3571,10 +3575,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>777517</v>
+        <v>777509</v>
       </c>
       <c r="R30" t="n">
-        <v>7298828</v>
+        <v>7298862</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,13 +3636,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088847</t>
+          <t>https://artportalen.se/Sighting/120088846</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120088849</v>
+        <v>120088847</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -3673,10 +3677,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>777511</v>
+        <v>777517</v>
       </c>
       <c r="R31" t="n">
-        <v>7298804</v>
+        <v>7298828</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,13 +3738,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088849</t>
+          <t>https://artportalen.se/Sighting/120088847</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120088850</v>
+        <v>120088849</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -3775,10 +3779,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>777502</v>
+        <v>777511</v>
       </c>
       <c r="R32" t="n">
-        <v>7298806</v>
+        <v>7298804</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3836,13 +3840,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088850</t>
+          <t>https://artportalen.se/Sighting/120088849</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120088851</v>
+        <v>120088850</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -3877,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>777457</v>
+        <v>777502</v>
       </c>
       <c r="R33" t="n">
-        <v>7298804</v>
+        <v>7298806</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3938,13 +3942,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088851</t>
+          <t>https://artportalen.se/Sighting/120088850</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120088852</v>
+        <v>120088851</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -3979,10 +3983,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>777427</v>
+        <v>777457</v>
       </c>
       <c r="R34" t="n">
-        <v>7298810</v>
+        <v>7298804</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4040,13 +4044,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088852</t>
+          <t>https://artportalen.se/Sighting/120088851</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120088853</v>
+        <v>120088852</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4081,10 +4085,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>777429</v>
+        <v>777427</v>
       </c>
       <c r="R35" t="n">
-        <v>7298824</v>
+        <v>7298810</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4142,13 +4146,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088853</t>
+          <t>https://artportalen.se/Sighting/120088852</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120088854</v>
+        <v>120088853</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4183,10 +4187,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>777398</v>
+        <v>777429</v>
       </c>
       <c r="R36" t="n">
-        <v>7298832</v>
+        <v>7298824</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,13 +4248,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088854</t>
+          <t>https://artportalen.se/Sighting/120088853</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120088855</v>
+        <v>120088854</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4285,10 +4289,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>777392</v>
+        <v>777398</v>
       </c>
       <c r="R37" t="n">
-        <v>7298835</v>
+        <v>7298832</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,13 +4350,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088855</t>
+          <t>https://artportalen.se/Sighting/120088854</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120088856</v>
+        <v>120088855</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4387,10 +4391,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>777378</v>
+        <v>777392</v>
       </c>
       <c r="R38" t="n">
-        <v>7298811</v>
+        <v>7298835</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4448,13 +4452,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088856</t>
+          <t>https://artportalen.se/Sighting/120088855</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120088857</v>
+        <v>120088856</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4489,10 +4493,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>777367</v>
+        <v>777378</v>
       </c>
       <c r="R39" t="n">
-        <v>7298814</v>
+        <v>7298811</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4550,13 +4554,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088857</t>
+          <t>https://artportalen.se/Sighting/120088856</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120088858</v>
+        <v>120088857</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -4591,10 +4595,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>777356</v>
+        <v>777367</v>
       </c>
       <c r="R40" t="n">
-        <v>7298837</v>
+        <v>7298814</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,13 +4656,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088858</t>
+          <t>https://artportalen.se/Sighting/120088857</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120088865</v>
+        <v>120088858</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -4687,20 +4691,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>777415</v>
+        <v>777356</v>
       </c>
       <c r="R41" t="n">
-        <v>7298849</v>
+        <v>7298837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4741,7 +4741,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4753,19 +4752,19 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088865</t>
+          <t>https://artportalen.se/Sighting/120088858</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120088866</v>
+        <v>120088865</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -4804,10 +4803,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>777389</v>
+        <v>777415</v>
       </c>
       <c r="R42" t="n">
-        <v>7298847</v>
+        <v>7298849</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,13 +4865,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088866</t>
+          <t>https://artportalen.se/Sighting/120088865</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120088867</v>
+        <v>120088866</v>
       </c>
       <c r="B43" t="n">
         <v>99118</v>
@@ -4911,10 +4910,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>777364</v>
+        <v>777389</v>
       </c>
       <c r="R43" t="n">
-        <v>7298811</v>
+        <v>7298847</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4973,13 +4972,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120088867</t>
+          <t>https://artportalen.se/Sighting/120088866</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120109444</v>
+        <v>120088867</v>
       </c>
       <c r="B44" t="n">
         <v>99118</v>
@@ -5008,16 +5007,20 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hundbergstjärn, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>777573</v>
+        <v>777364</v>
       </c>
       <c r="R44" t="n">
-        <v>7299187</v>
+        <v>7298811</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5044,12 +5047,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5058,30 +5061,31 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Filippa Ekroth</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109444</t>
+          <t>https://artportalen.se/Sighting/120088867</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120109445</v>
+        <v>120109444</v>
       </c>
       <c r="B45" t="n">
         <v>99118</v>
@@ -5116,10 +5120,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>777555</v>
+        <v>777573</v>
       </c>
       <c r="R45" t="n">
-        <v>7299109</v>
+        <v>7299187</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5177,13 +5181,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109445</t>
+          <t>https://artportalen.se/Sighting/120109444</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120109446</v>
+        <v>120109445</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5218,10 +5222,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>777434</v>
+        <v>777555</v>
       </c>
       <c r="R46" t="n">
-        <v>7298954</v>
+        <v>7299109</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5279,13 +5283,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109446</t>
+          <t>https://artportalen.se/Sighting/120109445</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120109447</v>
+        <v>120109446</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -5320,10 +5324,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>777398</v>
+        <v>777434</v>
       </c>
       <c r="R47" t="n">
-        <v>7298959</v>
+        <v>7298954</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5381,13 +5385,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109447</t>
+          <t>https://artportalen.se/Sighting/120109446</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120109448</v>
+        <v>120109447</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -5422,10 +5426,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>777417</v>
+        <v>777398</v>
       </c>
       <c r="R48" t="n">
-        <v>7298952</v>
+        <v>7298959</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,13 +5487,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109448</t>
+          <t>https://artportalen.se/Sighting/120109447</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120109449</v>
+        <v>120109448</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5524,10 +5528,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>777456</v>
+        <v>777417</v>
       </c>
       <c r="R49" t="n">
-        <v>7298953</v>
+        <v>7298952</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5585,13 +5589,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109449</t>
+          <t>https://artportalen.se/Sighting/120109448</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120109450</v>
+        <v>120109449</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -5626,10 +5630,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>777403</v>
+        <v>777456</v>
       </c>
       <c r="R50" t="n">
-        <v>7298895</v>
+        <v>7298953</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5687,13 +5691,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109450</t>
+          <t>https://artportalen.se/Sighting/120109449</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120109451</v>
+        <v>120109450</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -5728,10 +5732,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>777444</v>
+        <v>777403</v>
       </c>
       <c r="R51" t="n">
-        <v>7298882</v>
+        <v>7298895</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5789,13 +5793,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109451</t>
+          <t>https://artportalen.se/Sighting/120109450</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120109452</v>
+        <v>120109451</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -5830,10 +5834,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>777449</v>
+        <v>777444</v>
       </c>
       <c r="R52" t="n">
-        <v>7298879</v>
+        <v>7298882</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5891,13 +5895,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109452</t>
+          <t>https://artportalen.se/Sighting/120109451</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120109453</v>
+        <v>120109452</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -5932,10 +5936,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>777456</v>
+        <v>777449</v>
       </c>
       <c r="R53" t="n">
-        <v>7298884</v>
+        <v>7298879</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,13 +5997,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109453</t>
+          <t>https://artportalen.se/Sighting/120109452</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120109454</v>
+        <v>120109453</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6034,10 +6038,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>777458</v>
+        <v>777456</v>
       </c>
       <c r="R54" t="n">
-        <v>7298865</v>
+        <v>7298884</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6095,13 +6099,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109454</t>
+          <t>https://artportalen.se/Sighting/120109453</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120109455</v>
+        <v>120109454</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6136,10 +6140,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>777511</v>
+        <v>777458</v>
       </c>
       <c r="R55" t="n">
-        <v>7298851</v>
+        <v>7298865</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6197,13 +6201,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109455</t>
+          <t>https://artportalen.se/Sighting/120109454</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120109456</v>
+        <v>120109455</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6238,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>777582</v>
+        <v>777511</v>
       </c>
       <c r="R56" t="n">
-        <v>7299080</v>
+        <v>7298851</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6299,13 +6303,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109456</t>
+          <t>https://artportalen.se/Sighting/120109455</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120109457</v>
+        <v>120109456</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6340,10 +6344,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>777600</v>
+        <v>777582</v>
       </c>
       <c r="R57" t="n">
-        <v>7299114</v>
+        <v>7299080</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,13 +6405,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109457</t>
+          <t>https://artportalen.se/Sighting/120109456</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120109459</v>
+        <v>120109457</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -6442,10 +6446,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>777599</v>
+        <v>777600</v>
       </c>
       <c r="R58" t="n">
-        <v>7299147</v>
+        <v>7299114</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6503,13 +6507,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109459</t>
+          <t>https://artportalen.se/Sighting/120109457</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120109460</v>
+        <v>120109459</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -6544,10 +6548,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>777629</v>
+        <v>777599</v>
       </c>
       <c r="R59" t="n">
-        <v>7299201</v>
+        <v>7299147</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6605,13 +6609,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109460</t>
+          <t>https://artportalen.se/Sighting/120109459</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120109462</v>
+        <v>120109460</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -6646,10 +6650,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>777628</v>
+        <v>777629</v>
       </c>
       <c r="R60" t="n">
-        <v>7299215</v>
+        <v>7299201</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6707,13 +6711,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109462</t>
+          <t>https://artportalen.se/Sighting/120109460</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128404384</v>
+        <v>120109462</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -6748,13 +6752,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>777536</v>
+        <v>777628</v>
       </c>
       <c r="R61" t="n">
-        <v>7299152</v>
+        <v>7299215</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6778,12 +6782,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6798,24 +6802,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404384</t>
+          <t>https://artportalen.se/Sighting/120109462</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128404385</v>
+        <v>128404384</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -6850,10 +6854,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>777549</v>
+        <v>777536</v>
       </c>
       <c r="R62" t="n">
-        <v>7299126</v>
+        <v>7299152</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6911,13 +6915,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404385</t>
+          <t>https://artportalen.se/Sighting/128404384</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128404386</v>
+        <v>128404385</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -6952,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>777534</v>
+        <v>777549</v>
       </c>
       <c r="R63" t="n">
-        <v>7298905</v>
+        <v>7299126</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7013,13 +7017,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404386</t>
+          <t>https://artportalen.se/Sighting/128404385</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128404388</v>
+        <v>128404386</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7054,10 +7058,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>777495</v>
+        <v>777534</v>
       </c>
       <c r="R64" t="n">
-        <v>7298785</v>
+        <v>7298905</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7115,13 +7119,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404388</t>
+          <t>https://artportalen.se/Sighting/128404386</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128404389</v>
+        <v>128404388</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7156,10 +7160,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>777484</v>
+        <v>777495</v>
       </c>
       <c r="R65" t="n">
-        <v>7298784</v>
+        <v>7298785</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7217,13 +7221,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404389</t>
+          <t>https://artportalen.se/Sighting/128404388</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128404390</v>
+        <v>128404389</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7258,10 +7262,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>777504</v>
+        <v>777484</v>
       </c>
       <c r="R66" t="n">
-        <v>7298820</v>
+        <v>7298784</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7296,11 +7300,6 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Mycket stort bestånd</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7324,13 +7323,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404390</t>
+          <t>https://artportalen.se/Sighting/128404389</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128404392</v>
+        <v>128404390</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -7365,10 +7364,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>777498</v>
+        <v>777504</v>
       </c>
       <c r="R67" t="n">
-        <v>7298870</v>
+        <v>7298820</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7403,6 +7402,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Mycket stort bestånd</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7426,13 +7430,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404392</t>
+          <t>https://artportalen.se/Sighting/128404390</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128404393</v>
+        <v>128404392</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -7467,10 +7471,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>777550</v>
+        <v>777498</v>
       </c>
       <c r="R68" t="n">
-        <v>7298893</v>
+        <v>7298870</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7528,13 +7532,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404393</t>
+          <t>https://artportalen.se/Sighting/128404392</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128404394</v>
+        <v>128404393</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -7569,10 +7573,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>777610</v>
+        <v>777550</v>
       </c>
       <c r="R69" t="n">
-        <v>7299180</v>
+        <v>7298893</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7607,11 +7611,6 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Mycket rikligt bestånd</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7635,13 +7634,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404394</t>
+          <t>https://artportalen.se/Sighting/128404393</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128404395</v>
+        <v>128404394</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -7676,10 +7675,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>777614</v>
+        <v>777610</v>
       </c>
       <c r="R70" t="n">
-        <v>7299189</v>
+        <v>7299180</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7714,6 +7713,11 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Mycket rikligt bestånd</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7737,13 +7741,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404395</t>
+          <t>https://artportalen.se/Sighting/128404394</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128404398</v>
+        <v>128404395</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -7778,10 +7782,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>777628</v>
+        <v>777614</v>
       </c>
       <c r="R71" t="n">
-        <v>7299203</v>
+        <v>7299189</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7839,13 +7843,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404398</t>
+          <t>https://artportalen.se/Sighting/128404395</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128404399</v>
+        <v>128404398</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -7880,10 +7884,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>777619</v>
+        <v>777628</v>
       </c>
       <c r="R72" t="n">
-        <v>7299211</v>
+        <v>7299203</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7941,13 +7945,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404399</t>
+          <t>https://artportalen.se/Sighting/128404398</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128404402</v>
+        <v>128404399</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -7982,10 +7986,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>777608</v>
+        <v>777619</v>
       </c>
       <c r="R73" t="n">
-        <v>7299215</v>
+        <v>7299211</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8043,13 +8047,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404402</t>
+          <t>https://artportalen.se/Sighting/128404399</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128404403</v>
+        <v>128404402</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8084,10 +8088,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>777601</v>
+        <v>777608</v>
       </c>
       <c r="R74" t="n">
-        <v>7299235</v>
+        <v>7299215</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8145,13 +8149,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128404403</t>
+          <t>https://artportalen.se/Sighting/128404402</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129299331</v>
+        <v>128404403</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8186,10 +8190,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>777644</v>
+        <v>777601</v>
       </c>
       <c r="R75" t="n">
-        <v>7299199</v>
+        <v>7299235</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8216,17 +8220,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>1×2m</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8252,13 +8251,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299331</t>
+          <t>https://artportalen.se/Sighting/128404403</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129299332</v>
+        <v>129299331</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8293,10 +8292,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>777646</v>
+        <v>777644</v>
       </c>
       <c r="R76" t="n">
-        <v>7299185</v>
+        <v>7299199</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8331,6 +8330,11 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>1×2m</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8354,13 +8358,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299332</t>
+          <t>https://artportalen.se/Sighting/129299331</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129299333</v>
+        <v>129299332</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8395,7 +8399,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>777663</v>
+        <v>777646</v>
       </c>
       <c r="R77" t="n">
         <v>7299185</v>
@@ -8433,11 +8437,6 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>4×3m mycket riklig förekomst, mattbildande.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8461,13 +8460,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299333</t>
+          <t>https://artportalen.se/Sighting/129299332</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129299334</v>
+        <v>129299333</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -8502,10 +8501,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>777555</v>
+        <v>777663</v>
       </c>
       <c r="R78" t="n">
-        <v>7299104</v>
+        <v>7299185</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8542,7 +8541,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Mattbildande,riklig förekomst 1×2 m</t>
+          <t>4×3m mycket riklig förekomst, mattbildande.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8568,13 +8567,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299334</t>
+          <t>https://artportalen.se/Sighting/129299333</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129299336</v>
+        <v>129299334</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -8609,10 +8608,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>777522</v>
+        <v>777555</v>
       </c>
       <c r="R79" t="n">
-        <v>7299206</v>
+        <v>7299104</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8649,7 +8648,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Förekomst 1m× 2m</t>
+          <t>Mattbildande,riklig förekomst 1×2 m</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8675,38 +8674,38 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129299336</t>
+          <t>https://artportalen.se/Sighting/129299334</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120109443</v>
+        <v>129299336</v>
       </c>
       <c r="B80" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8716,13 +8715,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>777444</v>
+        <v>777522</v>
       </c>
       <c r="R80" t="n">
-        <v>7298925</v>
+        <v>7299206</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8746,12 +8745,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Förekomst 1m× 2m</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8766,27 +8770,27 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120109443</t>
+          <t>https://artportalen.se/Sighting/129299336</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128404377</v>
+        <v>120109443</v>
       </c>
       <c r="B81" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8794,16 +8798,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8818,13 +8822,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>777595</v>
+        <v>777444</v>
       </c>
       <c r="R81" t="n">
-        <v>7299107</v>
+        <v>7298925</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8848,12 +8852,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8868,16 +8872,118 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120109443</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128404377</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hundbergstjärn, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>777595</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7299107</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128404377</t>
         </is>
@@ -8965,6 +9071,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>120088861</v>
       </c>
       <c r="B14" t="n">
-        <v>85191</v>
+        <v>85193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>120088861</v>
       </c>
       <c r="B14" t="n">
-        <v>85193</v>
+        <v>85194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>120088861</v>
       </c>
       <c r="B14" t="n">
-        <v>85194</v>
+        <v>85195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>120088861</v>
       </c>
       <c r="B14" t="n">
-        <v>85195</v>
+        <v>85199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 7068-2023 artfynd.xlsx
+++ b/artfynd/A 7068-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>120088861</v>
       </c>
       <c r="B14" t="n">
-        <v>85199</v>
+        <v>85200</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
